--- a/database/event/3165/event_3165_evp_summary.xlsx
+++ b/database/event/3165/event_3165_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.2094</v>
+        <v>6.0299</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7206</v>
+        <v>0.8341</v>
       </c>
       <c r="D2" t="n">
-        <v>1.6831</v>
+        <v>1.9584</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2094</v>
+        <v>6.0299</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8918</v>
+        <v>3.7122</v>
       </c>
       <c r="G2" t="n">
         <v>2.3177</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8918</v>
+        <v>3.7122</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3439</v>
+        <v>3.0089</v>
       </c>
       <c r="J2" t="n">
         <v>2.3177</v>
@@ -529,7 +529,7 @@
         <v>67</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6616</v>
+        <v>5.3266</v>
       </c>
       <c r="N2" t="n">
         <v>128</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1567</v>
+        <v>5.917</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7133</v>
+        <v>0.8185</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6618</v>
+        <v>1.9134</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1567</v>
+        <v>5.917</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5773</v>
+        <v>3.3376</v>
       </c>
       <c r="G3" t="n">
         <v>2.5795</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5773</v>
+        <v>3.3376</v>
       </c>
       <c r="I3" t="n">
-        <v>2.089</v>
+        <v>2.7052</v>
       </c>
       <c r="J3" t="n">
         <v>2.5795</v>
@@ -575,7 +575,7 @@
         <v>103</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6685</v>
+        <v>5.2847</v>
       </c>
       <c r="N3" t="n">
         <v>157</v>
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.1563</v>
+        <v>5.4181</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7133</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6617</v>
+        <v>1.7147</v>
       </c>
       <c r="E4" t="n">
-        <v>5.1563</v>
+        <v>5.4181</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5024</v>
+        <v>0.7642</v>
       </c>
       <c r="G4" t="n">
         <v>4.6539</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5024</v>
+        <v>0.7642</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4072</v>
+        <v>0.6194</v>
       </c>
       <c r="J4" t="n">
         <v>4.6539</v>
@@ -621,7 +621,7 @@
         <v>124</v>
       </c>
       <c r="M4" t="n">
-        <v>5.0611</v>
+        <v>5.2733</v>
       </c>
       <c r="N4" t="n">
         <v>200</v>
@@ -634,28 +634,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.8736</v>
+        <v>5.3221</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6742</v>
+        <v>0.7362</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5475</v>
+        <v>1.6764</v>
       </c>
       <c r="E5" t="n">
-        <v>4.8736</v>
+        <v>5.3221</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4675</v>
+        <v>2.916</v>
       </c>
       <c r="G5" t="n">
         <v>2.4061</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4675</v>
+        <v>2.916</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.3635</v>
       </c>
       <c r="J5" t="n">
         <v>2.4061</v>
@@ -667,7 +667,7 @@
         <v>124</v>
       </c>
       <c r="M5" t="n">
-        <v>4.4061</v>
+        <v>4.769600000000001</v>
       </c>
       <c r="N5" t="n">
         <v>200</v>
@@ -680,28 +680,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.7778</v>
+        <v>4.3429</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5226</v>
+        <v>0.6007</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1048</v>
+        <v>1.2863</v>
       </c>
       <c r="E6" t="n">
-        <v>3.7778</v>
+        <v>4.3429</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3103</v>
+        <v>1.8754</v>
       </c>
       <c r="G6" t="n">
         <v>2.4675</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3103</v>
+        <v>1.8754</v>
       </c>
       <c r="I6" t="n">
-        <v>1.062</v>
+        <v>1.5201</v>
       </c>
       <c r="J6" t="n">
         <v>2.4675</v>
@@ -713,7 +713,7 @@
         <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5295</v>
+        <v>3.9876</v>
       </c>
       <c r="N6" t="n">
         <v>200</v>
@@ -726,28 +726,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.4829</v>
+        <v>2.7569</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3435</v>
+        <v>0.3814</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5817</v>
+        <v>0.6544</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4829</v>
+        <v>2.7569</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8089</v>
+        <v>1.0829</v>
       </c>
       <c r="G7" t="n">
         <v>1.674</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8089</v>
+        <v>1.0829</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.8777</v>
       </c>
       <c r="J7" t="n">
         <v>1.674</v>
@@ -759,7 +759,7 @@
         <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>2.3297</v>
+        <v>2.5517</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -772,28 +772,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.6952</v>
+        <v>2.2817</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2345</v>
+        <v>0.3156</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2635</v>
+        <v>0.4651</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6952</v>
+        <v>2.2817</v>
       </c>
       <c r="F8" t="n">
-        <v>2.3679</v>
+        <v>2.9544</v>
       </c>
       <c r="G8" t="n">
         <v>-0.6727</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3679</v>
+        <v>2.9544</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9192</v>
+        <v>2.3946</v>
       </c>
       <c r="J8" t="n">
         <v>-0.6727</v>
@@ -805,7 +805,7 @@
         <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>1.2465</v>
+        <v>1.7219</v>
       </c>
       <c r="N8" t="n">
         <v>157</v>
@@ -814,139 +814,139 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3971</v>
+        <v>1.9078</v>
       </c>
       <c r="C9" t="n">
-        <v>0.1933</v>
+        <v>0.2639</v>
       </c>
       <c r="D9" t="n">
-        <v>0.143</v>
+        <v>0.3162</v>
       </c>
       <c r="E9" t="n">
-        <v>1.3971</v>
+        <v>1.9078</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3971</v>
+        <v>1.9078</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.3971</v>
+        <v>1.9078</v>
       </c>
       <c r="I9" t="n">
-        <v>1.3971</v>
+        <v>1.9078</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>1.3971</v>
+        <v>1.9078</v>
       </c>
       <c r="N9" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.3961</v>
+        <v>1.8421</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1931</v>
+        <v>0.2548</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1426</v>
+        <v>0.29</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3961</v>
+        <v>1.8421</v>
       </c>
       <c r="F10" t="n">
-        <v>1.3961</v>
+        <v>2.8421</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3961</v>
+        <v>2.8421</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3961</v>
+        <v>2.3036</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K10" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3961</v>
+        <v>1.3036</v>
       </c>
       <c r="N10" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.3552</v>
+        <v>1.5765</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1875</v>
+        <v>0.2181</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1261</v>
+        <v>0.1842</v>
       </c>
       <c r="E11" t="n">
-        <v>1.3552</v>
+        <v>1.5765</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3552</v>
+        <v>1.5765</v>
       </c>
       <c r="G11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.3552</v>
+        <v>1.5765</v>
       </c>
       <c r="I11" t="n">
-        <v>1.9089</v>
+        <v>1.5765</v>
       </c>
       <c r="J11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="L11" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.9089</v>
+        <v>1.5765</v>
       </c>
       <c r="N11" t="n">
-        <v>126</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9487</v>
+        <v>1.2806</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1312</v>
+        <v>0.1771</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.0381</v>
+        <v>0.0663</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9487</v>
+        <v>1.2806</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9487</v>
+        <v>1.2806</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9487</v>
+        <v>1.2806</v>
       </c>
       <c r="I12" t="n">
-        <v>0.9487</v>
+        <v>1.2806</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.9487</v>
+        <v>1.2806</v>
       </c>
       <c r="N12" t="n">
         <v>82</v>
@@ -998,81 +998,81 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8955</v>
+        <v>0.9036</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1239</v>
+        <v>0.125</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0596</v>
+        <v>-0.0839</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8955</v>
+        <v>0.9036</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8272</v>
+        <v>0.9036</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0683</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8272</v>
+        <v>0.9036</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6705</v>
+        <v>0.9036</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0683</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="L13" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7388</v>
+        <v>0.9036</v>
       </c>
       <c r="N13" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8955</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1211</v>
+        <v>0.1239</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0677</v>
+        <v>-0.0871</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8754999999999999</v>
+        <v>0.8955</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2232</v>
+        <v>0.8272</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6523</v>
+        <v>0.0683</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2232</v>
+        <v>0.8272</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1809</v>
+        <v>0.6705</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6523</v>
+        <v>0.0683</v>
       </c>
       <c r="K14" t="n">
         <v>76</v>
@@ -1081,7 +1081,7 @@
         <v>124</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8331999999999999</v>
+        <v>0.7388</v>
       </c>
       <c r="N14" t="n">
         <v>200</v>
@@ -1090,173 +1090,173 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.757</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1047</v>
+        <v>0.1211</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.1156</v>
+        <v>-0.0951</v>
       </c>
       <c r="E15" t="n">
-        <v>0.757</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>0.757</v>
+        <v>0.2232</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.6523</v>
       </c>
       <c r="H15" t="n">
-        <v>0.757</v>
+        <v>0.2232</v>
       </c>
       <c r="I15" t="n">
-        <v>0.757</v>
+        <v>0.1809</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.6523</v>
       </c>
       <c r="K15" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M15" t="n">
-        <v>0.757</v>
+        <v>0.8331999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>Magisk</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.6367</v>
+        <v>0.7071</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0881</v>
+        <v>0.0978</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1641</v>
+        <v>-0.1622</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6367</v>
+        <v>0.7071</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2361</v>
+        <v>0.9742</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5994</v>
+        <v>-0.2671</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2361</v>
+        <v>0.9742</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0019</v>
+        <v>0.7896</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5994</v>
+        <v>-0.2671</v>
       </c>
       <c r="K16" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L16" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>0.4025</v>
+        <v>0.5225</v>
       </c>
       <c r="N16" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Magisk</t>
+          <t>devoduvek</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5879</v>
+        <v>0.6642</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0813</v>
+        <v>0.0919</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1839</v>
+        <v>-0.1793</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5879</v>
+        <v>0.6642</v>
       </c>
       <c r="F17" t="n">
-        <v>0.855</v>
+        <v>0.6642</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2671</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.855</v>
+        <v>0.6642</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2671</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L17" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4258999999999999</v>
+        <v>0.6642</v>
       </c>
       <c r="N17" t="n">
-        <v>126</v>
+        <v>85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EliGE</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.4136</v>
+        <v>0.6367</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0572</v>
+        <v>0.0881</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2543</v>
+        <v>-0.1902</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4136</v>
+        <v>0.6367</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1815</v>
+        <v>1.2361</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2321</v>
+        <v>-0.5994</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1815</v>
+        <v>1.2361</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1471</v>
+        <v>1.0019</v>
       </c>
       <c r="J18" t="n">
-        <v>0.2321</v>
+        <v>-0.5994</v>
       </c>
       <c r="K18" t="n">
         <v>61</v>
@@ -1265,7 +1265,7 @@
         <v>67</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3792</v>
+        <v>0.4025</v>
       </c>
       <c r="N18" t="n">
         <v>128</v>
@@ -1274,78 +1274,78 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>seang@res</t>
+          <t>EliGE</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.3202</v>
+        <v>0.4136</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0443</v>
+        <v>0.0572</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.292</v>
+        <v>-0.2791</v>
       </c>
       <c r="E19" t="n">
-        <v>0.3202</v>
+        <v>0.4136</v>
       </c>
       <c r="F19" t="n">
-        <v>0.3202</v>
+        <v>0.1815</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.2321</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3202</v>
+        <v>0.1815</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3202</v>
+        <v>0.1471</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>0.2321</v>
       </c>
       <c r="K19" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3202</v>
+        <v>0.3792</v>
       </c>
       <c r="N19" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>devoduvek</t>
+          <t>seang@res</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.2921</v>
+        <v>0.3202</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0404</v>
+        <v>0.0443</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3034</v>
+        <v>-0.3163</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2921</v>
+        <v>0.3202</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2921</v>
+        <v>0.3202</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2921</v>
+        <v>0.3202</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2921</v>
+        <v>0.3202</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2921</v>
+        <v>0.3202</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1376,7 +1376,7 @@
         <v>0.0366</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3144</v>
+        <v>-0.3385</v>
       </c>
       <c r="E21" t="n">
         <v>0.2647</v>
@@ -1422,7 +1422,7 @@
         <v>0.0174</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3707</v>
+        <v>-0.3939</v>
       </c>
       <c r="E22" t="n">
         <v>0.1255</v>
@@ -1468,7 +1468,7 @@
         <v>-0.0145</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4636</v>
+        <v>-0.4855</v>
       </c>
       <c r="E23" t="n">
         <v>-0.1045</v>
@@ -1514,7 +1514,7 @@
         <v>-0.018</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4738</v>
+        <v>-0.4957</v>
       </c>
       <c r="E24" t="n">
         <v>-0.1299</v>
@@ -1560,7 +1560,7 @@
         <v>-0.0193</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4776</v>
+        <v>-0.4994</v>
       </c>
       <c r="E25" t="n">
         <v>-0.1393</v>
@@ -1606,7 +1606,7 @@
         <v>-0.0198</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4792</v>
+        <v>-0.501</v>
       </c>
       <c r="E26" t="n">
         <v>-0.1432</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0284</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5042</v>
+        <v>-0.5256</v>
       </c>
       <c r="E27" t="n">
         <v>-0.205</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0395</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5367</v>
+        <v>-0.5577</v>
       </c>
       <c r="E28" t="n">
         <v>-0.2856</v>
@@ -1744,7 +1744,7 @@
         <v>-0.054</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.5995</v>
       </c>
       <c r="E29" t="n">
         <v>-0.3905</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0566</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.5866</v>
+        <v>-0.6069</v>
       </c>
       <c r="E30" t="n">
         <v>-0.4091</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0872</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.6949</v>
       </c>
       <c r="E31" t="n">
         <v>-0.6301</v>
@@ -1882,7 +1882,7 @@
         <v>-0.095</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.6989</v>
+        <v>-0.7176</v>
       </c>
       <c r="E32" t="n">
         <v>-0.6869</v>
@@ -1928,7 +1928,7 @@
         <v>-0.1027</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7214</v>
+        <v>-0.7398</v>
       </c>
       <c r="E33" t="n">
         <v>-0.7428</v>
@@ -1974,7 +1974,7 @@
         <v>-0.1119</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7483</v>
+        <v>-0.7663</v>
       </c>
       <c r="E34" t="n">
         <v>-0.8092</v>
@@ -2020,7 +2020,7 @@
         <v>-0.1161</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7603</v>
+        <v>-0.7782</v>
       </c>
       <c r="E35" t="n">
         <v>-0.8391</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1319</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8067</v>
+        <v>-0.8239</v>
       </c>
       <c r="E36" t="n">
         <v>-0.9538</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1483</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8546</v>
+        <v>-0.8712</v>
       </c>
       <c r="E37" t="n">
         <v>-1.0724</v>
@@ -2148,35 +2148,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.136</v>
+        <v>-1.1022</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1571</v>
+        <v>-0.1525</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.8803</v>
+        <v>-0.883</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.136</v>
+        <v>-1.1022</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.5914</v>
+        <v>-0.4996</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4554</v>
+        <v>-0.6026</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.5914</v>
+        <v>-0.4996</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.2899</v>
+        <v>-0.4049</v>
       </c>
       <c r="J38" t="n">
-        <v>0.4554</v>
+        <v>-0.6026</v>
       </c>
       <c r="K38" t="n">
         <v>80</v>
@@ -2185,7 +2185,7 @@
         <v>46</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.8345</v>
+        <v>-1.0075</v>
       </c>
       <c r="N38" t="n">
         <v>126</v>
@@ -2194,93 +2194,93 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2209</v>
+        <v>-1.136</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1689</v>
+        <v>-0.1571</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.9146</v>
+        <v>-0.8965</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2209</v>
+        <v>-1.136</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2209</v>
+        <v>-1.5914</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>0.4554</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2209</v>
+        <v>-1.5914</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2209</v>
+        <v>-1.2899</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>0.4554</v>
       </c>
       <c r="K39" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2209</v>
+        <v>-0.8345</v>
       </c>
       <c r="N39" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.3651</v>
+        <v>-1.2209</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1888</v>
+        <v>-0.1689</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9728</v>
+        <v>-0.9303</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.3651</v>
+        <v>-1.2209</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.7625</v>
+        <v>-1.2209</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.6026</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7625</v>
+        <v>-1.2209</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.618</v>
+        <v>-1.2209</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.6026</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L40" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2206</v>
+        <v>-1.2209</v>
       </c>
       <c r="N40" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41">
@@ -2296,7 +2296,7 @@
         <v>-0.1968</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.996</v>
+        <v>-1.0106</v>
       </c>
       <c r="E41" t="n">
         <v>-1.4224</v>

--- a/database/event/3165/event_3165_evp_summary.xlsx
+++ b/database/event/3165/event_3165_evp_summary.xlsx
@@ -492,185 +492,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>Stewie2K</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.0299</v>
+        <v>5.331</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8341</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9584</v>
+        <v>1.7687</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0299</v>
+        <v>5.331</v>
       </c>
       <c r="F2" t="n">
-        <v>3.7122</v>
+        <v>1.3801</v>
       </c>
       <c r="G2" t="n">
-        <v>2.3177</v>
+        <v>3.9509</v>
       </c>
       <c r="H2" t="n">
-        <v>3.7122</v>
+        <v>1.3801</v>
       </c>
       <c r="I2" t="n">
-        <v>3.0089</v>
+        <v>0.7176</v>
       </c>
       <c r="J2" t="n">
-        <v>2.3177</v>
+        <v>3.9509</v>
       </c>
       <c r="K2" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="L2" t="n">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>5.3266</v>
+        <v>4.6685</v>
       </c>
       <c r="N2" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.917</v>
+        <v>5.1275</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8185</v>
+        <v>0.7093</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9134</v>
+        <v>1.6768</v>
       </c>
       <c r="E3" t="n">
-        <v>5.917</v>
+        <v>5.1275</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3376</v>
+        <v>2.8234</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5795</v>
+        <v>2.3041</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3376</v>
+        <v>4.4615</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7052</v>
+        <v>2.3198</v>
       </c>
       <c r="J3" t="n">
-        <v>2.5795</v>
+        <v>2.3041</v>
       </c>
       <c r="K3" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L3" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="M3" t="n">
-        <v>5.2847</v>
+        <v>4.6239</v>
       </c>
       <c r="N3" t="n">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Stewie2K</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.4181</v>
+        <v>5.0014</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7495000000000001</v>
+        <v>0.6918</v>
       </c>
       <c r="D4" t="n">
-        <v>1.7147</v>
+        <v>1.6199</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4181</v>
+        <v>5.0014</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7642</v>
+        <v>3.0508</v>
       </c>
       <c r="G4" t="n">
-        <v>4.6539</v>
+        <v>1.9507</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7642</v>
+        <v>5.2627</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6194</v>
+        <v>2.7364</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6539</v>
+        <v>1.9507</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="L4" t="n">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="M4" t="n">
-        <v>5.2733</v>
+        <v>4.6871</v>
       </c>
       <c r="N4" t="n">
-        <v>200</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.3221</v>
+        <v>4.9806</v>
       </c>
       <c r="C5" t="n">
-        <v>0.7362</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6764</v>
+        <v>1.6105</v>
       </c>
       <c r="E5" t="n">
-        <v>5.3221</v>
+        <v>4.9806</v>
       </c>
       <c r="F5" t="n">
-        <v>2.916</v>
+        <v>2.8999</v>
       </c>
       <c r="G5" t="n">
-        <v>2.4061</v>
+        <v>2.0807</v>
       </c>
       <c r="H5" t="n">
-        <v>2.916</v>
+        <v>4.7312</v>
       </c>
       <c r="I5" t="n">
-        <v>2.3635</v>
+        <v>2.46</v>
       </c>
       <c r="J5" t="n">
-        <v>2.4061</v>
+        <v>2.0807</v>
       </c>
       <c r="K5" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L5" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>4.769600000000001</v>
+        <v>4.5407</v>
       </c>
       <c r="N5" t="n">
-        <v>200</v>
+        <v>157</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.3429</v>
+        <v>4.6471</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6007</v>
+        <v>0.6428</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2863</v>
+        <v>1.4599</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3429</v>
+        <v>4.6471</v>
       </c>
       <c r="F6" t="n">
-        <v>1.8754</v>
+        <v>2.3994</v>
       </c>
       <c r="G6" t="n">
-        <v>2.4675</v>
+        <v>2.2477</v>
       </c>
       <c r="H6" t="n">
-        <v>1.8754</v>
+        <v>2.9676</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5201</v>
+        <v>1.543</v>
       </c>
       <c r="J6" t="n">
-        <v>2.4675</v>
+        <v>2.2477</v>
       </c>
       <c r="K6" t="n">
         <v>76</v>
@@ -713,7 +713,7 @@
         <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9876</v>
+        <v>3.7907</v>
       </c>
       <c r="N6" t="n">
         <v>200</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.7569</v>
+        <v>3.2996</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3814</v>
+        <v>0.4564</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6544</v>
+        <v>0.8516</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7569</v>
+        <v>3.2996</v>
       </c>
       <c r="F7" t="n">
-        <v>1.0829</v>
+        <v>1.754</v>
       </c>
       <c r="G7" t="n">
-        <v>1.674</v>
+        <v>1.5456</v>
       </c>
       <c r="H7" t="n">
-        <v>1.0829</v>
+        <v>1.754</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8777</v>
+        <v>0.912</v>
       </c>
       <c r="J7" t="n">
-        <v>1.674</v>
+        <v>1.5456</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>2.5517</v>
+        <v>2.4576</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.2817</v>
+        <v>2.5161</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3156</v>
+        <v>0.348</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4651</v>
+        <v>0.4979</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2817</v>
+        <v>2.5161</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9544</v>
+        <v>2.7937</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6727</v>
+        <v>-0.2776</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9544</v>
+        <v>4.3569</v>
       </c>
       <c r="I8" t="n">
-        <v>2.3946</v>
+        <v>2.2654</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6727</v>
+        <v>-0.2776</v>
       </c>
       <c r="K8" t="n">
         <v>54</v>
@@ -805,7 +805,7 @@
         <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>1.7219</v>
+        <v>1.9878</v>
       </c>
       <c r="N8" t="n">
         <v>157</v>
@@ -814,47 +814,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9078</v>
+        <v>2.0384</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2639</v>
+        <v>0.282</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3162</v>
+        <v>0.2822</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9078</v>
+        <v>2.0384</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9078</v>
+        <v>1.623</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.4154</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9078</v>
+        <v>1.623</v>
       </c>
       <c r="I9" t="n">
-        <v>1.9078</v>
+        <v>0.8439</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.4154</v>
       </c>
       <c r="K9" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>1.9078</v>
+        <v>1.2593</v>
       </c>
       <c r="N9" t="n">
-        <v>85</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.8421</v>
+        <v>2.0371</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2548</v>
+        <v>0.2818</v>
       </c>
       <c r="D10" t="n">
-        <v>0.29</v>
+        <v>0.2816</v>
       </c>
       <c r="E10" t="n">
-        <v>1.8421</v>
+        <v>2.0371</v>
       </c>
       <c r="F10" t="n">
-        <v>2.8421</v>
+        <v>2.7056</v>
       </c>
       <c r="G10" t="n">
-        <v>-1</v>
+        <v>-0.6685</v>
       </c>
       <c r="H10" t="n">
-        <v>2.8421</v>
+        <v>4.0465</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3036</v>
+        <v>2.104</v>
       </c>
       <c r="J10" t="n">
-        <v>-1</v>
+        <v>-0.6685</v>
       </c>
       <c r="K10" t="n">
         <v>80</v>
@@ -897,7 +897,7 @@
         <v>46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3036</v>
+        <v>1.4355</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.5765</v>
+        <v>1.8965</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2181</v>
+        <v>0.2623</v>
       </c>
       <c r="D11" t="n">
-        <v>0.1842</v>
+        <v>0.2182</v>
       </c>
       <c r="E11" t="n">
-        <v>1.5765</v>
+        <v>1.8965</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5765</v>
+        <v>1.8965</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5765</v>
+        <v>1.8965</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5765</v>
+        <v>1.8965</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.5765</v>
+        <v>1.8965</v>
       </c>
       <c r="N11" t="n">
         <v>52</v>
@@ -952,127 +952,127 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Brehze</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.2806</v>
+        <v>1.8662</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1771</v>
+        <v>0.2581</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0663</v>
+        <v>0.2045</v>
       </c>
       <c r="E12" t="n">
-        <v>1.2806</v>
+        <v>1.8662</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2806</v>
+        <v>1.8662</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.2806</v>
+        <v>1.8662</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2806</v>
+        <v>1.8662</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2806</v>
+        <v>1.8662</v>
       </c>
       <c r="N12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>amanek</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9036</v>
+        <v>1.7514</v>
       </c>
       <c r="C13" t="n">
-        <v>0.125</v>
+        <v>0.2423</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0839</v>
+        <v>0.1527</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9036</v>
+        <v>1.7514</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9036</v>
+        <v>2.0098</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.2584</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9036</v>
+        <v>2.0098</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9036</v>
+        <v>1.045</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.2584</v>
       </c>
       <c r="K13" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9036</v>
+        <v>0.7866</v>
       </c>
       <c r="N13" t="n">
-        <v>85</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8955</v>
+        <v>1.5374</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1239</v>
+        <v>0.2127</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0871</v>
+        <v>0.056</v>
       </c>
       <c r="E14" t="n">
-        <v>0.8955</v>
+        <v>1.5374</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8272</v>
+        <v>0.7399</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0683</v>
+        <v>0.7975</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8272</v>
+        <v>0.7399</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6705</v>
+        <v>0.3847</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0683</v>
+        <v>0.7975</v>
       </c>
       <c r="K14" t="n">
         <v>76</v>
@@ -1081,7 +1081,7 @@
         <v>124</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7388</v>
+        <v>1.1822</v>
       </c>
       <c r="N14" t="n">
         <v>200</v>
@@ -1090,47 +1090,47 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>Brehze</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8754999999999999</v>
+        <v>1.533</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1211</v>
+        <v>0.2121</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.0951</v>
+        <v>0.0541</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8754999999999999</v>
+        <v>1.533</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2232</v>
+        <v>1.533</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6523</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2232</v>
+        <v>1.533</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1809</v>
+        <v>1.533</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6523</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="L15" t="n">
-        <v>124</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8331999999999999</v>
+        <v>1.533</v>
       </c>
       <c r="N15" t="n">
-        <v>200</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7071</v>
+        <v>1.4905</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0978</v>
+        <v>0.2062</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1622</v>
+        <v>0.0349</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7071</v>
+        <v>1.4905</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9742</v>
+        <v>1.7192</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2671</v>
+        <v>-0.2287</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9742</v>
+        <v>1.7192</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7896</v>
+        <v>0.8939</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2671</v>
+        <v>-0.2287</v>
       </c>
       <c r="K16" t="n">
         <v>80</v>
@@ -1173,7 +1173,7 @@
         <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5225</v>
+        <v>0.6652</v>
       </c>
       <c r="N16" t="n">
         <v>126</v>
@@ -1182,32 +1182,32 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>devoduvek</t>
+          <t>amanek</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.6642</v>
+        <v>1.1892</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0919</v>
+        <v>0.1645</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1793</v>
+        <v>-0.1011</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6642</v>
+        <v>1.1892</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6642</v>
+        <v>1.1892</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6642</v>
+        <v>1.1892</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6642</v>
+        <v>1.1892</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6642</v>
+        <v>1.1892</v>
       </c>
       <c r="N17" t="n">
         <v>85</v>
@@ -1228,47 +1228,47 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>devoduvek</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6367</v>
+        <v>0.862</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0881</v>
+        <v>0.1192</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1902</v>
+        <v>-0.2489</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6367</v>
+        <v>0.862</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2361</v>
+        <v>0.862</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.2361</v>
+        <v>0.862</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0019</v>
+        <v>0.862</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5994</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="L18" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4025</v>
+        <v>0.862</v>
       </c>
       <c r="N18" t="n">
-        <v>128</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.4136</v>
+        <v>0.7861</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0572</v>
+        <v>0.1087</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2791</v>
+        <v>-0.2831</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4136</v>
+        <v>0.7861</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1815</v>
+        <v>0.5462</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2321</v>
+        <v>0.2399</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1815</v>
+        <v>0.5462</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1471</v>
+        <v>0.284</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2321</v>
+        <v>0.2399</v>
       </c>
       <c r="K19" t="n">
         <v>61</v>
@@ -1311,7 +1311,7 @@
         <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.3792</v>
+        <v>0.5239</v>
       </c>
       <c r="N19" t="n">
         <v>128</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.3202</v>
+        <v>0.5767</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0443</v>
+        <v>0.0798</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3163</v>
+        <v>-0.3777</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3202</v>
+        <v>0.5767</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3202</v>
+        <v>0.5767</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3202</v>
+        <v>0.5767</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3202</v>
+        <v>0.5767</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3202</v>
+        <v>0.5767</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1366,262 +1366,262 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>ShahZaM</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2647</v>
+        <v>0.2976</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0366</v>
+        <v>0.0412</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3385</v>
+        <v>-0.5037</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2647</v>
+        <v>0.2976</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2647</v>
+        <v>0.2976</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2647</v>
+        <v>0.2976</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2647</v>
+        <v>0.2976</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2647</v>
+        <v>0.2976</v>
       </c>
       <c r="N21" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.1255</v>
+        <v>0.2497</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0174</v>
+        <v>0.0345</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3939</v>
+        <v>-0.5253</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1255</v>
+        <v>0.2497</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1255</v>
+        <v>0.2497</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1255</v>
+        <v>0.2497</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1255</v>
+        <v>0.2497</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1255</v>
+        <v>0.2497</v>
       </c>
       <c r="N22" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AnJ</t>
+          <t>AZR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-0.1045</v>
+        <v>0.2247</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.0145</v>
+        <v>0.0311</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.4855</v>
+        <v>-0.5366</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1045</v>
+        <v>0.2247</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1045</v>
+        <v>1.4107</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>-1.186</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1045</v>
+        <v>1.4107</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.1045</v>
+        <v>0.7335</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1.186</v>
       </c>
       <c r="K23" t="n">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1045</v>
+        <v>-0.4524999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>82</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ShahZaM</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-0.1299</v>
+        <v>0.1393</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.018</v>
+        <v>0.0193</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4957</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.1299</v>
+        <v>0.1393</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1299</v>
+        <v>0.773</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.6337</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.1299</v>
+        <v>0.773</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1299</v>
+        <v>0.4019</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.6337</v>
       </c>
       <c r="K24" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1299</v>
+        <v>-0.2318000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>126</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1393</v>
+        <v>0.1217</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0193</v>
+        <v>0.0168</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4994</v>
+        <v>-0.5831</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1393</v>
+        <v>0.1217</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.1393</v>
+        <v>0.1217</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1393</v>
+        <v>0.1217</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.1393</v>
+        <v>0.1217</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.1393</v>
+        <v>0.1217</v>
       </c>
       <c r="N25" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>AnJ</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1432</v>
+        <v>0.073</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0198</v>
+        <v>0.0101</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.501</v>
+        <v>-0.6051</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1432</v>
+        <v>0.073</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.1432</v>
+        <v>0.073</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.1432</v>
+        <v>0.073</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1432</v>
+        <v>0.073</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1432</v>
+        <v>0.073</v>
       </c>
       <c r="N26" t="n">
         <v>82</v>
@@ -1642,32 +1642,32 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FugLy</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.205</v>
+        <v>0.0227</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0284</v>
+        <v>0.0031</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5256</v>
+        <v>-0.6278</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.205</v>
+        <v>0.0227</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.205</v>
+        <v>0.0227</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.205</v>
+        <v>0.0227</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.205</v>
+        <v>0.0227</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.205</v>
+        <v>0.0227</v>
       </c>
       <c r="N27" t="n">
         <v>82</v>
@@ -1688,78 +1688,78 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>FugLy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.2856</v>
+        <v>-0.0867</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0395</v>
+        <v>-0.012</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5577</v>
+        <v>-0.6772</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.2856</v>
+        <v>-0.0867</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.1409</v>
+        <v>-0.0867</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8552999999999999</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1409</v>
+        <v>-0.0867</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.9247</v>
+        <v>-0.0867</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8552999999999999</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>54</v>
+        <v>82</v>
       </c>
       <c r="L28" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.06940000000000002</v>
+        <v>-0.0867</v>
       </c>
       <c r="N28" t="n">
-        <v>157</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PKL</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.3905</v>
+        <v>-0.1071</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.054</v>
+        <v>-0.0148</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.5995</v>
+        <v>-0.6864</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.3905</v>
+        <v>-0.1071</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.3905</v>
+        <v>-0.1071</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.3905</v>
+        <v>-0.1071</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.3905</v>
+        <v>-0.1071</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.3905</v>
+        <v>-0.1071</v>
       </c>
       <c r="N29" t="n">
         <v>60</v>
@@ -1780,139 +1780,139 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>stanislaw</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.4091</v>
+        <v>-0.2689</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0566</v>
+        <v>-0.0372</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6069</v>
+        <v>-0.7594</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.4091</v>
+        <v>-0.2689</v>
       </c>
       <c r="F30" t="n">
-        <v>0.484</v>
+        <v>0.0356</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.8931</v>
+        <v>-0.3045</v>
       </c>
       <c r="H30" t="n">
-        <v>0.484</v>
+        <v>0.0356</v>
       </c>
       <c r="I30" t="n">
-        <v>0.3923</v>
+        <v>0.0185</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.8931</v>
+        <v>-0.3045</v>
       </c>
       <c r="K30" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L30" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5008</v>
+        <v>-0.286</v>
       </c>
       <c r="N30" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>PKL</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.6301</v>
+        <v>-0.28</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0872</v>
+        <v>-0.0387</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.6949</v>
+        <v>-0.7644</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.6301</v>
+        <v>-0.28</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.6301</v>
+        <v>-0.28</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.6301</v>
+        <v>-0.28</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.6301</v>
+        <v>-0.28</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.6301</v>
+        <v>-0.28</v>
       </c>
       <c r="N31" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AZR</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.6869</v>
+        <v>-0.3977</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.095</v>
+        <v>-0.055</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7176</v>
+        <v>-0.8176</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.6869</v>
+        <v>-0.3977</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7129</v>
+        <v>-0.3977</v>
       </c>
       <c r="G32" t="n">
-        <v>-1.3998</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.7129</v>
+        <v>-0.3977</v>
       </c>
       <c r="I32" t="n">
-        <v>0.5778</v>
+        <v>-0.3977</v>
       </c>
       <c r="J32" t="n">
-        <v>-1.3998</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L32" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.822</v>
+        <v>-0.3977</v>
       </c>
       <c r="N32" t="n">
-        <v>157</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33">
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.7428</v>
+        <v>-0.4836</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.1027</v>
+        <v>-0.0669</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.7398</v>
+        <v>-0.8563</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.7428</v>
+        <v>-0.4836</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.7428</v>
+        <v>-0.4836</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.7428</v>
+        <v>-0.4836</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.7428</v>
+        <v>-0.4836</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.7428</v>
+        <v>-0.4836</v>
       </c>
       <c r="N33" t="n">
         <v>60</v>
@@ -1964,265 +1964,265 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stanislaw</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.8092</v>
+        <v>-0.5332</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.1119</v>
+        <v>-0.0738</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.7663</v>
+        <v>-0.8787</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.8092</v>
+        <v>-0.5332</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.1453</v>
+        <v>-0.5332</v>
       </c>
       <c r="G34" t="n">
-        <v>-0.6639</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1453</v>
+        <v>-0.5332</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1178</v>
+        <v>-0.5332</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.6639</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L34" t="n">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7817000000000001</v>
+        <v>-0.5332</v>
       </c>
       <c r="N34" t="n">
-        <v>128</v>
+        <v>52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8391</v>
+        <v>-0.623</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.1161</v>
+        <v>-0.0862</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.7782</v>
+        <v>-0.9193</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8391</v>
+        <v>-0.623</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8391</v>
+        <v>-0.623</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8391</v>
+        <v>-0.623</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8391</v>
+        <v>-0.623</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8391</v>
+        <v>-0.623</v>
       </c>
       <c r="N35" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.9538</v>
+        <v>-0.7214</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1319</v>
+        <v>-0.0998</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.8239</v>
+        <v>-0.9637</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.9538</v>
+        <v>-0.7214</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.9538</v>
+        <v>-0.7214</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.9538</v>
+        <v>-0.7214</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.9538</v>
+        <v>-0.7214</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.9538</v>
+        <v>-0.7214</v>
       </c>
       <c r="N36" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.0724</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1483</v>
+        <v>-0.1021</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.8712</v>
+        <v>-0.9714</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.0724</v>
+        <v>-0.7383999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.0724</v>
+        <v>-1.5649</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>0.8265</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.0724</v>
+        <v>-1.5649</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.0724</v>
+        <v>-0.8137</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>0.8265</v>
       </c>
       <c r="K37" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.0724</v>
+        <v>0.01280000000000003</v>
       </c>
       <c r="N37" t="n">
-        <v>52</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.1022</v>
+        <v>-0.773</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1525</v>
+        <v>-0.1069</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.883</v>
+        <v>-0.987</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.1022</v>
+        <v>-0.773</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.4996</v>
+        <v>-0.773</v>
       </c>
       <c r="G38" t="n">
-        <v>-0.6026</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.4996</v>
+        <v>-0.773</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4049</v>
+        <v>-0.773</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.6026</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L38" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0075</v>
+        <v>-0.773</v>
       </c>
       <c r="N38" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.136</v>
+        <v>-0.8944</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1571</v>
+        <v>-0.1237</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.8965</v>
+        <v>-1.0418</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.136</v>
+        <v>-0.8944</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.5914</v>
+        <v>-0.487</v>
       </c>
       <c r="G39" t="n">
-        <v>0.4554</v>
+        <v>-0.4074</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.5914</v>
+        <v>-0.487</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2899</v>
+        <v>-0.2532</v>
       </c>
       <c r="J39" t="n">
-        <v>0.4554</v>
+        <v>-0.4074</v>
       </c>
       <c r="K39" t="n">
         <v>80</v>
@@ -2231,7 +2231,7 @@
         <v>46</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.8345</v>
+        <v>-0.6606</v>
       </c>
       <c r="N39" t="n">
         <v>126</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.2209</v>
+        <v>-1.7947</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1689</v>
+        <v>-0.2483</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.9303</v>
+        <v>-1.4482</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.2209</v>
+        <v>-1.7947</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.2209</v>
+        <v>-1.784</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>-0.0107</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.2209</v>
+        <v>-1.784</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.2209</v>
+        <v>-0.9276</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>-0.0107</v>
       </c>
       <c r="K40" t="n">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.2209</v>
+        <v>-0.9383</v>
       </c>
       <c r="N40" t="n">
-        <v>82</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.4224</v>
+        <v>-1.8704</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.1968</v>
+        <v>-0.2587</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.0106</v>
+        <v>-1.4824</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.4224</v>
+        <v>-1.8704</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.309</v>
+        <v>-2.3058</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.1134</v>
+        <v>0.4354</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.309</v>
+        <v>-2.3058</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.061</v>
+        <v>-1.1989</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.1134</v>
+        <v>0.4354</v>
       </c>
       <c r="K41" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L41" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1744</v>
+        <v>-0.7635000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0823</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.4432</v>
+        <v>-1.8106</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06560000000000001</v>
+        <v>-0.0823</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.4432</v>
+        <v>-1.8106</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.65</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4918</v>
+        <v>-0.34</v>
       </c>
       <c r="J4" t="n">
-        <v>-10.8196</v>
+        <v>-7.48</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.57</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6119</v>
+        <v>-0.4142</v>
       </c>
       <c r="J5" t="n">
-        <v>-13.4618</v>
+        <v>-9.112399999999999</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8464</v>
+        <v>-0.5829</v>
       </c>
       <c r="J6" t="n">
-        <v>-18.6208</v>
+        <v>-12.8238</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.149</v>
+        <v>1.1172</v>
       </c>
       <c r="J7" t="n">
-        <v>25.278</v>
+        <v>24.5784</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9529</v>
+        <v>1.0001</v>
       </c>
       <c r="J8" t="n">
-        <v>20.9638</v>
+        <v>22.0022</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.39</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8712</v>
+        <v>0.9489</v>
       </c>
       <c r="J9" t="n">
-        <v>19.1664</v>
+        <v>20.8758</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.8461</v>
       </c>
       <c r="J10" t="n">
-        <v>16.423</v>
+        <v>18.6142</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6536</v>
+        <v>0.7575</v>
       </c>
       <c r="J11" t="n">
-        <v>14.3792</v>
+        <v>16.665</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4924</v>
+        <v>0.5759</v>
       </c>
       <c r="J12" t="n">
-        <v>17.234</v>
+        <v>20.1565</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2553</v>
+        <v>0.2674</v>
       </c>
       <c r="J13" t="n">
-        <v>8.935499999999999</v>
+        <v>9.359</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.3342</v>
+        <v>-0.2102</v>
       </c>
       <c r="J14" t="n">
-        <v>-11.697</v>
+        <v>-7.357</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.3647</v>
+        <v>-0.2304</v>
       </c>
       <c r="J15" t="n">
-        <v>-12.7645</v>
+        <v>-8.064</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.66</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5585</v>
+        <v>-0.3655</v>
       </c>
       <c r="J16" t="n">
-        <v>-19.5475</v>
+        <v>-12.7925</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.2222</v>
+        <v>1.1413</v>
       </c>
       <c r="J17" t="n">
-        <v>42.777</v>
+        <v>39.9455</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5611</v>
+        <v>0.5835</v>
       </c>
       <c r="J18" t="n">
-        <v>19.6385</v>
+        <v>20.4225</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.19</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4924</v>
+        <v>0.5366</v>
       </c>
       <c r="J19" t="n">
-        <v>17.234</v>
+        <v>18.781</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.13</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3218</v>
+        <v>0.3847</v>
       </c>
       <c r="J20" t="n">
-        <v>11.263</v>
+        <v>13.4645</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.261</v>
+        <v>-0.182</v>
       </c>
       <c r="J21" t="n">
-        <v>-9.135</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.01</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1582</v>
+        <v>0.7741</v>
       </c>
       <c r="J22" t="n">
-        <v>22.0058</v>
+        <v>14.7079</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.62</v>
       </c>
       <c r="I23" t="n">
-        <v>0.761</v>
+        <v>0.5515</v>
       </c>
       <c r="J23" t="n">
-        <v>14.459</v>
+        <v>10.4785</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.27</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3161</v>
+        <v>0.3329</v>
       </c>
       <c r="J24" t="n">
-        <v>6.0059</v>
+        <v>6.3251</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3161</v>
+        <v>0.3329</v>
       </c>
       <c r="J25" t="n">
-        <v>6.0059</v>
+        <v>6.3251</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.26</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3033</v>
+        <v>0.3233</v>
       </c>
       <c r="J26" t="n">
-        <v>5.7627</v>
+        <v>6.1427</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1303</v>
+        <v>0.0806</v>
       </c>
       <c r="J27" t="n">
-        <v>2.4757</v>
+        <v>1.5314</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0226</v>
+        <v>-0.0194</v>
       </c>
       <c r="J28" t="n">
-        <v>0.4294</v>
+        <v>-0.3686</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1815</v>
+        <v>-0.1655</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.4485</v>
+        <v>-3.1445</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.29</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.9612000000000001</v>
+        <v>-0.6726</v>
       </c>
       <c r="J30" t="n">
-        <v>-18.2628</v>
+        <v>-12.7794</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.0544</v>
+        <v>-0.7482</v>
       </c>
       <c r="J31" t="n">
-        <v>-20.0336</v>
+        <v>-14.2158</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6373</v>
+        <v>0.595</v>
       </c>
       <c r="J32" t="n">
-        <v>13.3833</v>
+        <v>12.495</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.98</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0014</v>
+        <v>-0.024</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.0294</v>
+        <v>-0.504</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.73</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.4541</v>
+        <v>-0.2936</v>
       </c>
       <c r="J34" t="n">
-        <v>-9.536099999999999</v>
+        <v>-6.1656</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.4541</v>
+        <v>-0.2936</v>
       </c>
       <c r="J35" t="n">
-        <v>-9.536099999999999</v>
+        <v>-6.1656</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.63</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5886</v>
+        <v>-0.3884</v>
       </c>
       <c r="J36" t="n">
-        <v>-12.3606</v>
+        <v>-8.1564</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.61</v>
       </c>
       <c r="I37" t="n">
-        <v>1.3855</v>
+        <v>0.9801</v>
       </c>
       <c r="J37" t="n">
-        <v>29.0955</v>
+        <v>20.5821</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.44</v>
       </c>
       <c r="I38" t="n">
-        <v>1.0452</v>
+        <v>0.7698</v>
       </c>
       <c r="J38" t="n">
-        <v>21.9492</v>
+        <v>16.1658</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.9363</v>
+        <v>0.7066</v>
       </c>
       <c r="J39" t="n">
-        <v>19.6623</v>
+        <v>14.8386</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1919</v>
+        <v>0.2772</v>
       </c>
       <c r="J40" t="n">
-        <v>4.0299</v>
+        <v>5.8212</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.1581</v>
+        <v>-0.0747</v>
       </c>
       <c r="J41" t="n">
-        <v>-3.3201</v>
+        <v>-1.5687</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.36</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6254</v>
+        <v>0.5844</v>
       </c>
       <c r="J42" t="n">
-        <v>16.8858</v>
+        <v>15.7788</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.95</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.08260000000000001</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.2302</v>
+        <v>-1.863</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3914</v>
+        <v>-0.249</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.5678</v>
+        <v>-6.723</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.4203</v>
+        <v>-0.2686</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.3481</v>
+        <v>-7.2522</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.74</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4486</v>
+        <v>-0.2881</v>
       </c>
       <c r="J46" t="n">
-        <v>-12.1122</v>
+        <v>-7.7787</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.58</v>
       </c>
       <c r="I47" t="n">
-        <v>1.379</v>
+        <v>0.9693000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>37.233</v>
+        <v>26.1711</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.48</v>
       </c>
       <c r="I48" t="n">
-        <v>1.1819</v>
+        <v>0.842</v>
       </c>
       <c r="J48" t="n">
-        <v>31.9113</v>
+        <v>22.734</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.0149</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>0.4023</v>
+        <v>2.2815</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1818</v>
+        <v>-0.1036</v>
       </c>
       <c r="J50" t="n">
-        <v>-4.9086</v>
+        <v>-2.7972</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.4197</v>
+        <v>-0.3444</v>
       </c>
       <c r="J51" t="n">
-        <v>-11.3319</v>
+        <v>-9.2988</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.59</v>
       </c>
       <c r="I52" t="n">
-        <v>1.3399</v>
+        <v>0.9524</v>
       </c>
       <c r="J52" t="n">
-        <v>30.8177</v>
+        <v>21.9052</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>1.0369</v>
+        <v>0.7673</v>
       </c>
       <c r="J53" t="n">
-        <v>23.8487</v>
+        <v>17.6479</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.4</v>
       </c>
       <c r="I54" t="n">
-        <v>0.9495</v>
+        <v>0.7171</v>
       </c>
       <c r="J54" t="n">
-        <v>21.8385</v>
+        <v>16.4933</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5192</v>
+        <v>0.4961</v>
       </c>
       <c r="J55" t="n">
-        <v>11.9416</v>
+        <v>11.4103</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.3318</v>
+        <v>-0.2465</v>
       </c>
       <c r="J56" t="n">
-        <v>-7.6314</v>
+        <v>-5.6695</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5194</v>
+        <v>0.4996</v>
       </c>
       <c r="J57" t="n">
-        <v>11.9462</v>
+        <v>11.4908</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.85</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2031</v>
+        <v>-0.1645</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.6713</v>
+        <v>-3.7835</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.3366</v>
+        <v>-0.2333</v>
       </c>
       <c r="J59" t="n">
-        <v>-7.7418</v>
+        <v>-5.3659</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.5234</v>
+        <v>-0.3469</v>
       </c>
       <c r="J60" t="n">
-        <v>-12.0382</v>
+        <v>-7.9787</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.42</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.8290999999999999</v>
+        <v>-0.5695</v>
       </c>
       <c r="J61" t="n">
-        <v>-19.0693</v>
+        <v>-13.0985</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.13</v>
       </c>
       <c r="I62" t="n">
-        <v>2.032</v>
+        <v>1.5918</v>
       </c>
       <c r="J62" t="n">
-        <v>46.736</v>
+        <v>36.6114</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.52</v>
       </c>
       <c r="I63" t="n">
-        <v>1.2109</v>
+        <v>0.87</v>
       </c>
       <c r="J63" t="n">
-        <v>27.8507</v>
+        <v>20.01</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.07</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1065</v>
+        <v>0.1896</v>
       </c>
       <c r="J64" t="n">
-        <v>2.4495</v>
+        <v>4.3608</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2153</v>
+        <v>-0.1291</v>
       </c>
       <c r="J65" t="n">
-        <v>-4.9519</v>
+        <v>-2.9693</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.647</v>
       </c>
       <c r="J66" t="n">
-        <v>-16.2403</v>
+        <v>-14.881</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.064</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.472</v>
+        <v>-1.4766</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.064</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.472</v>
+        <v>-1.4766</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.95</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.064</v>
+        <v>-0.06419999999999999</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.472</v>
+        <v>-1.4766</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.85</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.266</v>
+        <v>-0.1741</v>
       </c>
       <c r="J70" t="n">
-        <v>-6.118</v>
+        <v>-4.0043</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.7</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4942</v>
+        <v>-0.3216</v>
       </c>
       <c r="J71" t="n">
-        <v>-11.3666</v>
+        <v>-7.3968</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.5848</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>15.2048</v>
+        <v>18.3066</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2287</v>
+        <v>0.2469</v>
       </c>
       <c r="J73" t="n">
-        <v>5.9462</v>
+        <v>6.4194</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2113</v>
+        <v>0.2263</v>
       </c>
       <c r="J74" t="n">
-        <v>5.4938</v>
+        <v>5.8838</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.83</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.339</v>
+        <v>-0.2084</v>
       </c>
       <c r="J75" t="n">
-        <v>-8.814</v>
+        <v>-5.4184</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.62</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6211</v>
+        <v>-0.4107</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.1486</v>
+        <v>-10.6782</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.46</v>
       </c>
       <c r="I77" t="n">
-        <v>1.1431</v>
+        <v>1.0909</v>
       </c>
       <c r="J77" t="n">
-        <v>29.7206</v>
+        <v>28.3634</v>
       </c>
     </row>
     <row r="78">
@@ -5509,10 +5509,10 @@
         <v>1.27</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7223000000000001</v>
+        <v>0.7251</v>
       </c>
       <c r="J79" t="n">
-        <v>18.7798</v>
+        <v>18.8526</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.0165</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J80" t="n">
-        <v>0.429</v>
+        <v>2.223</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.5291</v>
+        <v>-0.4595</v>
       </c>
       <c r="J81" t="n">
-        <v>-13.7566</v>
+        <v>-11.947</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.64</v>
+        <v>0.7798</v>
       </c>
       <c r="J82" t="n">
-        <v>16</v>
+        <v>19.495</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0129</v>
+        <v>-0.0277</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.3225</v>
+        <v>-0.6925</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1902</v>
+        <v>-0.1251</v>
       </c>
       <c r="J84" t="n">
-        <v>-4.755</v>
+        <v>-3.1275</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.68</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5289</v>
+        <v>-0.3447</v>
       </c>
       <c r="J85" t="n">
-        <v>-13.2225</v>
+        <v>-8.6175</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.63</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5938</v>
+        <v>-0.3916</v>
       </c>
       <c r="J86" t="n">
-        <v>-14.845</v>
+        <v>-9.789999999999999</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>1.1411</v>
+        <v>1.09</v>
       </c>
       <c r="J87" t="n">
-        <v>28.5275</v>
+        <v>27.25</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9506</v>
+        <v>0.9497</v>
       </c>
       <c r="J88" t="n">
-        <v>23.765</v>
+        <v>23.7425</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1468</v>
+        <v>0.2149</v>
       </c>
       <c r="J89" t="n">
-        <v>3.67</v>
+        <v>5.3725</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1468</v>
+        <v>0.2149</v>
       </c>
       <c r="J90" t="n">
-        <v>3.67</v>
+        <v>5.3725</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.03</v>
       </c>
       <c r="I91" t="n">
-        <v>0.0149</v>
+        <v>0.08450000000000001</v>
       </c>
       <c r="J91" t="n">
-        <v>0.3725</v>
+        <v>2.1125</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.06</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1947</v>
+        <v>0.1886</v>
       </c>
       <c r="J92" t="n">
-        <v>4.8675</v>
+        <v>4.715</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.01</v>
       </c>
       <c r="I93" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.0594</v>
       </c>
       <c r="J93" t="n">
-        <v>2.1725</v>
+        <v>1.485</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.0264</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.21</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3865</v>
+        <v>-0.2469</v>
       </c>
       <c r="J95" t="n">
-        <v>-9.6625</v>
+        <v>-6.1725</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.68</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5266</v>
+        <v>-0.3434</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.165</v>
+        <v>-8.585000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.03</v>
       </c>
       <c r="I97" t="n">
-        <v>2.0422</v>
+        <v>1.7598</v>
       </c>
       <c r="J97" t="n">
-        <v>51.055</v>
+        <v>43.995</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6207</v>
+        <v>0.6874</v>
       </c>
       <c r="J98" t="n">
-        <v>15.5175</v>
+        <v>17.185</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3107</v>
+        <v>0.3932</v>
       </c>
       <c r="J99" t="n">
-        <v>7.7675</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.0849</v>
+        <v>0.1648</v>
       </c>
       <c r="J100" t="n">
-        <v>2.1225</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.4704</v>
+        <v>-0.3934</v>
       </c>
       <c r="J101" t="n">
-        <v>-11.76</v>
+        <v>-9.835000000000001</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.66</v>
       </c>
       <c r="I102" t="n">
-        <v>1.5447</v>
+        <v>1.3524</v>
       </c>
       <c r="J102" t="n">
-        <v>46.341</v>
+        <v>40.572</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.47</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1767</v>
+        <v>1.1102</v>
       </c>
       <c r="J103" t="n">
-        <v>35.301</v>
+        <v>33.306</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2222</v>
+        <v>0.2811</v>
       </c>
       <c r="J104" t="n">
-        <v>6.666</v>
+        <v>8.433</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2851</v>
+        <v>-0.2094</v>
       </c>
       <c r="J105" t="n">
-        <v>-8.553000000000001</v>
+        <v>-6.282</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.67</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.0136</v>
+        <v>-0.9902</v>
       </c>
       <c r="J106" t="n">
-        <v>-30.408</v>
+        <v>-29.706</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2155</v>
+        <v>0.2204</v>
       </c>
       <c r="J107" t="n">
-        <v>6.465</v>
+        <v>6.612</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0271</v>
+        <v>-0.0314</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.8129999999999999</v>
+        <v>-0.9419999999999999</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1243</v>
+        <v>-0.083</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.729</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.92</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1682</v>
+        <v>-0.1058</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.046</v>
+        <v>-3.174</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.79</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.3835</v>
+        <v>-0.242</v>
       </c>
       <c r="J111" t="n">
-        <v>-11.505</v>
+        <v>-7.26</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.36</v>
       </c>
       <c r="I112" t="n">
-        <v>0.632</v>
+        <v>0.7689</v>
       </c>
       <c r="J112" t="n">
-        <v>14.536</v>
+        <v>17.6847</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1566</v>
+        <v>0.1417</v>
       </c>
       <c r="J113" t="n">
-        <v>3.6018</v>
+        <v>3.2591</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.85</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2755</v>
+        <v>-0.1763</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.3365</v>
+        <v>-4.0549</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.73</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4579</v>
+        <v>-0.2954</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.5317</v>
+        <v>-6.7942</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.52</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7272999999999999</v>
+        <v>-0.4913</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.7279</v>
+        <v>-11.2999</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>1.3484</v>
+        <v>1.2269</v>
       </c>
       <c r="J117" t="n">
-        <v>31.0132</v>
+        <v>28.2187</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.5</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1909</v>
+        <v>1.1271</v>
       </c>
       <c r="J118" t="n">
-        <v>27.3907</v>
+        <v>25.9233</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5265</v>
+        <v>0.5973000000000001</v>
       </c>
       <c r="J119" t="n">
-        <v>12.1095</v>
+        <v>13.7379</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.0688</v>
       </c>
       <c r="J120" t="n">
-        <v>-0.1932</v>
+        <v>1.5824</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.2031</v>
+        <v>-0.1193</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.6713</v>
+        <v>-2.7439</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.11</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2651</v>
+        <v>0.2822</v>
       </c>
       <c r="J122" t="n">
-        <v>9.5436</v>
+        <v>10.1592</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.09379999999999999</v>
+        <v>0.077</v>
       </c>
       <c r="J123" t="n">
-        <v>3.3768</v>
+        <v>2.772</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.208</v>
+        <v>-0.1284</v>
       </c>
       <c r="J124" t="n">
-        <v>-7.488</v>
+        <v>-4.6224</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.87</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.2602</v>
+        <v>-0.1607</v>
       </c>
       <c r="J125" t="n">
-        <v>-9.3672</v>
+        <v>-5.7852</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3245</v>
+        <v>-0.2022</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.682</v>
+        <v>-7.2792</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>1.1429</v>
+        <v>1.0877</v>
       </c>
       <c r="J127" t="n">
-        <v>41.1444</v>
+        <v>39.1572</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4844</v>
+        <v>0.4942</v>
       </c>
       <c r="J128" t="n">
-        <v>17.4384</v>
+        <v>17.7912</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.11</v>
       </c>
       <c r="I129" t="n">
-        <v>0.2905</v>
+        <v>0.3403</v>
       </c>
       <c r="J129" t="n">
-        <v>10.458</v>
+        <v>12.2508</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1035</v>
+        <v>0.1632</v>
       </c>
       <c r="J130" t="n">
-        <v>3.726</v>
+        <v>5.8752</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.1059</v>
+        <v>-0.0374</v>
       </c>
       <c r="J131" t="n">
-        <v>-3.8124</v>
+        <v>-1.3464</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.1295</v>
+        <v>1.0738</v>
       </c>
       <c r="J132" t="n">
-        <v>40.662</v>
+        <v>38.6568</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.11</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3812</v>
+        <v>0.3576</v>
       </c>
       <c r="J133" t="n">
-        <v>13.7232</v>
+        <v>12.8736</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1636</v>
+        <v>-0.1092</v>
       </c>
       <c r="J134" t="n">
-        <v>-5.8896</v>
+        <v>-3.9312</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.2027</v>
+        <v>-0.1463</v>
       </c>
       <c r="J135" t="n">
-        <v>-7.2972</v>
+        <v>-5.2668</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5906</v>
+        <v>-0.5342</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.2616</v>
+        <v>-19.2312</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>0.8954</v>
+        <v>1.0822</v>
       </c>
       <c r="J137" t="n">
-        <v>32.2344</v>
+        <v>38.9592</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3307</v>
+        <v>0.3924</v>
       </c>
       <c r="J138" t="n">
-        <v>11.9052</v>
+        <v>14.1264</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1327</v>
+        <v>0.1878</v>
       </c>
       <c r="J139" t="n">
-        <v>4.7772</v>
+        <v>6.7608</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.06</v>
       </c>
       <c r="I140" t="n">
-        <v>0.0944</v>
+        <v>0.1456</v>
       </c>
       <c r="J140" t="n">
-        <v>3.3984</v>
+        <v>5.2416</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.7063</v>
+        <v>-0.4753</v>
       </c>
       <c r="J141" t="n">
-        <v>-25.4268</v>
+        <v>-17.1108</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.23</v>
       </c>
       <c r="I142" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J142" t="n">
-        <v>43.2453</v>
+        <v>38.5098</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1974</v>
+        <v>1.1497</v>
       </c>
       <c r="J143" t="n">
-        <v>25.1454</v>
+        <v>24.1437</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.5508</v>
+        <v>0.6604</v>
       </c>
       <c r="J144" t="n">
-        <v>11.5668</v>
+        <v>13.8684</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.1584</v>
+        <v>0.2528</v>
       </c>
       <c r="J145" t="n">
-        <v>3.3264</v>
+        <v>5.3088</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.3535</v>
+        <v>-0.2666</v>
       </c>
       <c r="J146" t="n">
-        <v>-7.4235</v>
+        <v>-5.5986</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.96</v>
       </c>
       <c r="I147" t="n">
-        <v>0.0049</v>
+        <v>-0.0296</v>
       </c>
       <c r="J147" t="n">
-        <v>0.1029</v>
+        <v>-0.6216</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.82</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2435</v>
+        <v>-0.1925</v>
       </c>
       <c r="J148" t="n">
-        <v>-5.1135</v>
+        <v>-4.0425</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2956</v>
+        <v>-0.2222</v>
       </c>
       <c r="J149" t="n">
-        <v>-6.2076</v>
+        <v>-4.6662</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.67</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.5023</v>
+        <v>-0.3345</v>
       </c>
       <c r="J150" t="n">
-        <v>-10.5483</v>
+        <v>-7.0245</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.5861</v>
+        <v>-0.3909</v>
       </c>
       <c r="J151" t="n">
-        <v>-12.3081</v>
+        <v>-8.2089</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.66</v>
       </c>
       <c r="I152" t="n">
-        <v>0.9445</v>
+        <v>1.1276</v>
       </c>
       <c r="J152" t="n">
-        <v>27.3905</v>
+        <v>32.7004</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.03</v>
       </c>
       <c r="I153" t="n">
-        <v>0.09719999999999999</v>
+        <v>0.0936</v>
       </c>
       <c r="J153" t="n">
-        <v>2.8188</v>
+        <v>2.7144</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.99</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0311</v>
+        <v>-0.02</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.9019</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.3812</v>
+        <v>-0.2378</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.0548</v>
+        <v>-6.8962</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.47</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.7969000000000001</v>
+        <v>-0.5451</v>
       </c>
       <c r="J156" t="n">
-        <v>-23.1101</v>
+        <v>-15.8079</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>1.4944</v>
+        <v>1.3195</v>
       </c>
       <c r="J157" t="n">
-        <v>43.3376</v>
+        <v>38.2655</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.1</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3842</v>
+        <v>0.3428</v>
       </c>
       <c r="J158" t="n">
-        <v>11.1418</v>
+        <v>9.9412</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.07</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2899</v>
+        <v>0.2546</v>
       </c>
       <c r="J159" t="n">
-        <v>8.4071</v>
+        <v>7.3834</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.9555</v>
+        <v>-0.928</v>
       </c>
       <c r="J160" t="n">
-        <v>-27.7095</v>
+        <v>-26.912</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.0214</v>
+        <v>-1.0007</v>
       </c>
       <c r="J161" t="n">
-        <v>-29.6206</v>
+        <v>-29.0203</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>1.5285</v>
+        <v>1.3498</v>
       </c>
       <c r="J162" t="n">
-        <v>36.684</v>
+        <v>32.3952</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1628</v>
+        <v>1.1214</v>
       </c>
       <c r="J163" t="n">
-        <v>27.9072</v>
+        <v>26.9136</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.8499</v>
+        <v>0.913</v>
       </c>
       <c r="J164" t="n">
-        <v>20.3976</v>
+        <v>21.912</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.3556</v>
+        <v>0.4524</v>
       </c>
       <c r="J165" t="n">
-        <v>8.5344</v>
+        <v>10.8576</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.07</v>
       </c>
       <c r="I166" t="n">
-        <v>0.08890000000000001</v>
+        <v>0.1765</v>
       </c>
       <c r="J166" t="n">
-        <v>2.1336</v>
+        <v>4.236</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.96</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0004</v>
+        <v>-0.0325</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1303</v>
+        <v>-0.1193</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.1272</v>
+        <v>-2.8632</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.83</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2331</v>
+        <v>-0.1841</v>
       </c>
       <c r="J169" t="n">
-        <v>-5.5944</v>
+        <v>-4.4184</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-0.3552</v>
       </c>
       <c r="J170" t="n">
-        <v>-12.8352</v>
+        <v>-8.524800000000001</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.58</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6293</v>
+        <v>-0.4208</v>
       </c>
       <c r="J171" t="n">
-        <v>-15.1032</v>
+        <v>-10.0992</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3165/event_3165_evp_summary.xlsx
+++ b/database/event/3165/event_3165_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.331</v>
+        <v>5.3618</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.7417</v>
       </c>
       <c r="D2" t="n">
-        <v>1.7687</v>
+        <v>1.8166</v>
       </c>
       <c r="E2" t="n">
-        <v>5.331</v>
+        <v>5.3618</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3801</v>
+        <v>1.275</v>
       </c>
       <c r="G2" t="n">
-        <v>3.9509</v>
+        <v>4.0868</v>
       </c>
       <c r="H2" t="n">
-        <v>1.3801</v>
+        <v>1.275</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7176</v>
+        <v>0.6885</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9509</v>
+        <v>4.0868</v>
       </c>
       <c r="K2" t="n">
         <v>76</v>
@@ -529,7 +529,7 @@
         <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6685</v>
+        <v>4.775300000000001</v>
       </c>
       <c r="N2" t="n">
         <v>200</v>
@@ -538,93 +538,93 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.1275</v>
+        <v>5.227</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7093</v>
+        <v>0.723</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6768</v>
+        <v>1.7552</v>
       </c>
       <c r="E3" t="n">
-        <v>5.1275</v>
+        <v>5.227</v>
       </c>
       <c r="F3" t="n">
-        <v>2.8234</v>
+        <v>3.044</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3041</v>
+        <v>2.1831</v>
       </c>
       <c r="H3" t="n">
-        <v>4.4615</v>
+        <v>5.149</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3198</v>
+        <v>2.7804</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3041</v>
+        <v>2.1831</v>
       </c>
       <c r="K3" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="L3" t="n">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6239</v>
+        <v>4.9635</v>
       </c>
       <c r="N3" t="n">
-        <v>200</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0014</v>
+        <v>5.0501</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6918</v>
+        <v>0.6986</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6199</v>
+        <v>1.6747</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0014</v>
+        <v>5.0501</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0508</v>
+        <v>2.739</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9507</v>
+        <v>2.3111</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2627</v>
+        <v>4.1427</v>
       </c>
       <c r="I4" t="n">
-        <v>2.7364</v>
+        <v>2.237</v>
       </c>
       <c r="J4" t="n">
-        <v>1.9507</v>
+        <v>2.3111</v>
       </c>
       <c r="K4" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="L4" t="n">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="M4" t="n">
-        <v>4.6871</v>
+        <v>4.5481</v>
       </c>
       <c r="N4" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5">
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.9806</v>
+        <v>5.0423</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6975</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6105</v>
+        <v>1.6712</v>
       </c>
       <c r="E5" t="n">
-        <v>4.9806</v>
+        <v>5.0423</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8999</v>
+        <v>2.8318</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0807</v>
+        <v>2.2105</v>
       </c>
       <c r="H5" t="n">
-        <v>4.7312</v>
+        <v>4.449</v>
       </c>
       <c r="I5" t="n">
-        <v>2.46</v>
+        <v>2.4024</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0807</v>
+        <v>2.2105</v>
       </c>
       <c r="K5" t="n">
         <v>54</v>
@@ -667,7 +667,7 @@
         <v>103</v>
       </c>
       <c r="M5" t="n">
-        <v>4.5407</v>
+        <v>4.6129</v>
       </c>
       <c r="N5" t="n">
         <v>157</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.6471</v>
+        <v>4.7592</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6428</v>
+        <v>0.6583</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4599</v>
+        <v>1.5423</v>
       </c>
       <c r="E6" t="n">
-        <v>4.6471</v>
+        <v>4.7592</v>
       </c>
       <c r="F6" t="n">
-        <v>2.3994</v>
+        <v>2.4848</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2477</v>
+        <v>2.2744</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9676</v>
+        <v>3.3041</v>
       </c>
       <c r="I6" t="n">
-        <v>1.543</v>
+        <v>1.7842</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2477</v>
+        <v>2.2744</v>
       </c>
       <c r="K6" t="n">
         <v>76</v>
@@ -713,7 +713,7 @@
         <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7907</v>
+        <v>4.0586</v>
       </c>
       <c r="N6" t="n">
         <v>200</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.2996</v>
+        <v>3.389</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4564</v>
+        <v>0.4688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8516</v>
+        <v>0.9185</v>
       </c>
       <c r="E7" t="n">
-        <v>3.2996</v>
+        <v>3.389</v>
       </c>
       <c r="F7" t="n">
-        <v>1.754</v>
+        <v>1.6465</v>
       </c>
       <c r="G7" t="n">
-        <v>1.5456</v>
+        <v>1.7425</v>
       </c>
       <c r="H7" t="n">
-        <v>1.754</v>
+        <v>1.6465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.912</v>
+        <v>0.8891</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5456</v>
+        <v>1.7425</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>2.4576</v>
+        <v>2.6316</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.5161</v>
+        <v>2.4804</v>
       </c>
       <c r="C8" t="n">
-        <v>0.348</v>
+        <v>0.3431</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4979</v>
+        <v>0.5049</v>
       </c>
       <c r="E8" t="n">
-        <v>2.5161</v>
+        <v>2.4804</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7937</v>
+        <v>2.7139</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2776</v>
+        <v>-0.2335</v>
       </c>
       <c r="H8" t="n">
-        <v>4.3569</v>
+        <v>4.0599</v>
       </c>
       <c r="I8" t="n">
-        <v>2.2654</v>
+        <v>2.1923</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2776</v>
+        <v>-0.2335</v>
       </c>
       <c r="K8" t="n">
         <v>54</v>
@@ -805,7 +805,7 @@
         <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9878</v>
+        <v>1.9588</v>
       </c>
       <c r="N8" t="n">
         <v>157</v>
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.0384</v>
+        <v>1.9619</v>
       </c>
       <c r="C9" t="n">
-        <v>0.282</v>
+        <v>0.2714</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2822</v>
+        <v>0.2689</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0384</v>
+        <v>1.9619</v>
       </c>
       <c r="F9" t="n">
-        <v>1.623</v>
+        <v>1.5424</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4154</v>
+        <v>0.4195</v>
       </c>
       <c r="H9" t="n">
-        <v>1.623</v>
+        <v>1.5424</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8439</v>
+        <v>0.8329</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4154</v>
+        <v>0.4195</v>
       </c>
       <c r="K9" t="n">
         <v>76</v>
@@ -851,7 +851,7 @@
         <v>124</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2593</v>
+        <v>1.2524</v>
       </c>
       <c r="N9" t="n">
         <v>200</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.0371</v>
+        <v>1.9262</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2818</v>
+        <v>0.2664</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2816</v>
+        <v>0.2526</v>
       </c>
       <c r="E10" t="n">
-        <v>2.0371</v>
+        <v>1.9262</v>
       </c>
       <c r="F10" t="n">
-        <v>2.7056</v>
+        <v>2.6253</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6685</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0465</v>
+        <v>3.7677</v>
       </c>
       <c r="I10" t="n">
-        <v>2.104</v>
+        <v>2.0345</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6685</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>80</v>
@@ -897,7 +897,7 @@
         <v>46</v>
       </c>
       <c r="M10" t="n">
-        <v>1.4355</v>
+        <v>1.3354</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -906,185 +906,185 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8965</v>
+        <v>1.8477</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2623</v>
+        <v>0.2556</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2182</v>
+        <v>0.2169</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8965</v>
+        <v>1.8477</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8965</v>
+        <v>1.8477</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8965</v>
+        <v>1.8477</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8965</v>
+        <v>1.8477</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8965</v>
+        <v>1.8477</v>
       </c>
       <c r="N11" t="n">
-        <v>52</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8662</v>
+        <v>1.8232</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2581</v>
+        <v>0.2522</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2045</v>
+        <v>0.2058</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8662</v>
+        <v>1.8232</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8662</v>
+        <v>1.8232</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8662</v>
+        <v>1.8232</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8662</v>
+        <v>1.8232</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8662</v>
+        <v>1.8232</v>
       </c>
       <c r="N12" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>jdm64</t>
+          <t>RUSH</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7514</v>
+        <v>1.6576</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2423</v>
+        <v>0.2293</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1527</v>
+        <v>0.1304</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7514</v>
+        <v>1.6576</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0098</v>
+        <v>0.7578</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2584</v>
+        <v>0.8998</v>
       </c>
       <c r="H13" t="n">
-        <v>2.0098</v>
+        <v>0.7578</v>
       </c>
       <c r="I13" t="n">
-        <v>1.045</v>
+        <v>0.4092</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2584</v>
+        <v>0.8998</v>
       </c>
       <c r="K13" t="n">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="L13" t="n">
-        <v>67</v>
+        <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7866</v>
+        <v>1.309</v>
       </c>
       <c r="N13" t="n">
-        <v>128</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>RUSH</t>
+          <t>jdm64</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5374</v>
+        <v>1.6186</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2127</v>
+        <v>0.2239</v>
       </c>
       <c r="D14" t="n">
-        <v>0.056</v>
+        <v>0.1126</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5374</v>
+        <v>1.6186</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7399</v>
+        <v>1.8824</v>
       </c>
       <c r="G14" t="n">
-        <v>0.7975</v>
+        <v>-0.2638</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7399</v>
+        <v>1.8824</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3847</v>
+        <v>1.0165</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7975</v>
+        <v>-0.2638</v>
       </c>
       <c r="K14" t="n">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="L14" t="n">
-        <v>124</v>
+        <v>67</v>
       </c>
       <c r="M14" t="n">
-        <v>1.1822</v>
+        <v>0.7526999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>200</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15">
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.533</v>
+        <v>1.4286</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2121</v>
+        <v>0.1976</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0541</v>
+        <v>0.0261</v>
       </c>
       <c r="E15" t="n">
-        <v>1.533</v>
+        <v>1.4286</v>
       </c>
       <c r="F15" t="n">
-        <v>1.533</v>
+        <v>1.4286</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.533</v>
+        <v>1.4286</v>
       </c>
       <c r="I15" t="n">
-        <v>1.533</v>
+        <v>1.4286</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.533</v>
+        <v>1.4286</v>
       </c>
       <c r="N15" t="n">
         <v>82</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.4905</v>
+        <v>1.2708</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2062</v>
+        <v>0.1758</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0349</v>
+        <v>-0.0457</v>
       </c>
       <c r="E16" t="n">
-        <v>1.4905</v>
+        <v>1.2708</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7192</v>
+        <v>1.5315</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2287</v>
+        <v>-0.2607</v>
       </c>
       <c r="H16" t="n">
-        <v>1.7192</v>
+        <v>1.5315</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8939</v>
+        <v>0.827</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2287</v>
+        <v>-0.2607</v>
       </c>
       <c r="K16" t="n">
         <v>80</v>
@@ -1173,7 +1173,7 @@
         <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6652</v>
+        <v>0.5663</v>
       </c>
       <c r="N16" t="n">
         <v>126</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1892</v>
+        <v>1.1804</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1645</v>
+        <v>0.1633</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1011</v>
+        <v>-0.08690000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1892</v>
+        <v>1.1804</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1892</v>
+        <v>1.1804</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1892</v>
+        <v>1.1804</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1892</v>
+        <v>1.1804</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1892</v>
+        <v>1.1804</v>
       </c>
       <c r="N17" t="n">
         <v>85</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.862</v>
+        <v>0.8308</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1192</v>
+        <v>0.1149</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2489</v>
+        <v>-0.246</v>
       </c>
       <c r="E18" t="n">
-        <v>0.862</v>
+        <v>0.8308</v>
       </c>
       <c r="F18" t="n">
-        <v>0.862</v>
+        <v>0.8308</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.862</v>
+        <v>0.8308</v>
       </c>
       <c r="I18" t="n">
-        <v>0.862</v>
+        <v>0.8308</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.862</v>
+        <v>0.8308</v>
       </c>
       <c r="N18" t="n">
         <v>85</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7861</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1087</v>
+        <v>0.1074</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2831</v>
+        <v>-0.2706</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7861</v>
+        <v>0.7766999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5462</v>
+        <v>0.532</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2399</v>
+        <v>0.2447</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5462</v>
+        <v>0.532</v>
       </c>
       <c r="I19" t="n">
-        <v>0.284</v>
+        <v>0.2873</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2399</v>
+        <v>0.2447</v>
       </c>
       <c r="K19" t="n">
         <v>61</v>
@@ -1311,7 +1311,7 @@
         <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5239</v>
+        <v>0.532</v>
       </c>
       <c r="N19" t="n">
         <v>128</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5767</v>
+        <v>0.5591</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0798</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3777</v>
+        <v>-0.3697</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5767</v>
+        <v>0.5591</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5767</v>
+        <v>0.5591</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5767</v>
+        <v>0.5591</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5767</v>
+        <v>0.5591</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5767</v>
+        <v>0.5591</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2976</v>
+        <v>0.2895</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0412</v>
+        <v>0.04</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.5037</v>
+        <v>-0.4924</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2976</v>
+        <v>0.2895</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2976</v>
+        <v>0.2895</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2976</v>
+        <v>0.2895</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2976</v>
+        <v>0.2895</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2976</v>
+        <v>0.2895</v>
       </c>
       <c r="N21" t="n">
         <v>85</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2497</v>
+        <v>0.2344</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0345</v>
+        <v>0.0324</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5253</v>
+        <v>-0.5175</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2497</v>
+        <v>0.2344</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2497</v>
+        <v>0.2344</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2497</v>
+        <v>0.2344</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2497</v>
+        <v>0.2344</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2497</v>
+        <v>0.2344</v>
       </c>
       <c r="N22" t="n">
         <v>60</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2247</v>
+        <v>0.2233</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0311</v>
+        <v>0.0309</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5366</v>
+        <v>-0.5226</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2247</v>
+        <v>0.2233</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4107</v>
+        <v>1.3776</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.186</v>
+        <v>-1.1543</v>
       </c>
       <c r="H23" t="n">
-        <v>1.4107</v>
+        <v>1.3776</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7335</v>
+        <v>0.7439</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.186</v>
+        <v>-1.1543</v>
       </c>
       <c r="K23" t="n">
         <v>54</v>
@@ -1495,7 +1495,7 @@
         <v>103</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4524999999999999</v>
+        <v>-0.4104000000000001</v>
       </c>
       <c r="N23" t="n">
         <v>157</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>koosta</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1393</v>
+        <v>0.1184</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0193</v>
+        <v>0.0164</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-0.5703</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1393</v>
+        <v>0.1184</v>
       </c>
       <c r="F24" t="n">
-        <v>0.773</v>
+        <v>0.1184</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.6337</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.773</v>
+        <v>0.1184</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4019</v>
+        <v>0.1184</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.6337</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>80</v>
+        <v>52</v>
       </c>
       <c r="L24" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.2318000000000001</v>
+        <v>0.1184</v>
       </c>
       <c r="N24" t="n">
-        <v>126</v>
+        <v>52</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>koosta</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1217</v>
+        <v>0.1037</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0168</v>
+        <v>0.0143</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5831</v>
+        <v>-0.577</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1217</v>
+        <v>0.1037</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1217</v>
+        <v>0.7541</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.6504</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1217</v>
+        <v>0.7541</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1217</v>
+        <v>0.4072</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.6504</v>
       </c>
       <c r="K25" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1217</v>
+        <v>-0.2432</v>
       </c>
       <c r="N25" t="n">
-        <v>52</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26">
@@ -1600,28 +1600,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.073</v>
+        <v>0.0345</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0101</v>
+        <v>0.0048</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6051</v>
+        <v>-0.6085</v>
       </c>
       <c r="E26" t="n">
-        <v>0.073</v>
+        <v>0.0345</v>
       </c>
       <c r="F26" t="n">
-        <v>0.073</v>
+        <v>0.0345</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.073</v>
+        <v>0.0345</v>
       </c>
       <c r="I26" t="n">
-        <v>0.073</v>
+        <v>0.0345</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.073</v>
+        <v>0.0345</v>
       </c>
       <c r="N26" t="n">
         <v>82</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0227</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0031</v>
+        <v>-0.0013</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6278</v>
+        <v>-0.6284</v>
       </c>
       <c r="E27" t="n">
-        <v>0.0227</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0227</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0227</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0227</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.0227</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="N27" t="n">
         <v>82</v>
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.0867</v>
+        <v>-0.101</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.012</v>
+        <v>-0.014</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6772</v>
+        <v>-0.6702</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.0867</v>
+        <v>-0.101</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0867</v>
+        <v>-0.101</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0867</v>
+        <v>-0.101</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0867</v>
+        <v>-0.101</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.0867</v>
+        <v>-0.101</v>
       </c>
       <c r="N28" t="n">
         <v>82</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1071</v>
+        <v>-0.1221</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0148</v>
+        <v>-0.0169</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6864</v>
+        <v>-0.6798</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1071</v>
+        <v>-0.1221</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1071</v>
+        <v>-0.1221</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1071</v>
+        <v>-0.1221</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1071</v>
+        <v>-0.1221</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1071</v>
+        <v>-0.1221</v>
       </c>
       <c r="N29" t="n">
         <v>60</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2689</v>
+        <v>-0.2322</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0372</v>
+        <v>-0.0321</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7594</v>
+        <v>-0.7299</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2689</v>
+        <v>-0.2322</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0356</v>
+        <v>0.0733</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3045</v>
+        <v>-0.3055</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0356</v>
+        <v>0.0733</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0185</v>
+        <v>0.0396</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3045</v>
+        <v>-0.3055</v>
       </c>
       <c r="K30" t="n">
         <v>61</v>
@@ -1817,7 +1817,7 @@
         <v>67</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.286</v>
+        <v>-0.2659</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.28</v>
+        <v>-0.3137</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0387</v>
+        <v>-0.0434</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7644</v>
+        <v>-0.767</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.28</v>
+        <v>-0.3137</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.28</v>
+        <v>-0.3137</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.28</v>
+        <v>-0.3137</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.28</v>
+        <v>-0.3137</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.28</v>
+        <v>-0.3137</v>
       </c>
       <c r="N31" t="n">
         <v>60</v>
@@ -1872,277 +1872,277 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3977</v>
+        <v>-0.3544</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.055</v>
+        <v>-0.049</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.8176</v>
+        <v>-0.7855</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3977</v>
+        <v>-0.3544</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3977</v>
+        <v>-1.2985</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3977</v>
+        <v>-1.2985</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3977</v>
+        <v>-0.7012</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>0.9441000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3977</v>
+        <v>0.2429</v>
       </c>
       <c r="N32" t="n">
-        <v>52</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SHOOWTiME</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4836</v>
+        <v>-0.3966</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0669</v>
+        <v>-0.0549</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8563</v>
+        <v>-0.8047</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4836</v>
+        <v>-0.3966</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4836</v>
+        <v>-0.3966</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4836</v>
+        <v>-0.3966</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4836</v>
+        <v>-0.3966</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4836</v>
+        <v>-0.3966</v>
       </c>
       <c r="N33" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ethan</t>
+          <t>SHOOWTiME</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5332</v>
+        <v>-0.5135</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0738</v>
+        <v>-0.07099999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8787</v>
+        <v>-0.858</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5332</v>
+        <v>-0.5135</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5332</v>
+        <v>-0.5135</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5332</v>
+        <v>-0.5135</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5332</v>
+        <v>-0.5135</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5332</v>
+        <v>-0.5135</v>
       </c>
       <c r="N34" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>chelo</t>
+          <t>Ethan</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.623</v>
+        <v>-0.5618</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0862</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9193</v>
+        <v>-0.8799</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.623</v>
+        <v>-0.5618</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.623</v>
+        <v>-0.5618</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.623</v>
+        <v>-0.5618</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.623</v>
+        <v>-0.5618</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.623</v>
+        <v>-0.5618</v>
       </c>
       <c r="N35" t="n">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FNS</t>
+          <t>chelo</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.7214</v>
+        <v>-0.6508</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0998</v>
+        <v>-0.09</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9637</v>
+        <v>-0.9205</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.7214</v>
+        <v>-0.6508</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.7214</v>
+        <v>-0.6508</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.7214</v>
+        <v>-0.6508</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.7214</v>
+        <v>-0.6508</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.7214</v>
+        <v>-0.6508</v>
       </c>
       <c r="N36" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>FNS</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.7399</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1021</v>
+        <v>-0.1023</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9714</v>
+        <v>-0.961</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7383999999999999</v>
+        <v>-0.7399</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.5649</v>
+        <v>-0.7399</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8265</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.5649</v>
+        <v>-0.7399</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8137</v>
+        <v>-0.7399</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8265</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L37" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01280000000000003</v>
+        <v>-0.7399</v>
       </c>
       <c r="N37" t="n">
-        <v>157</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.773</v>
+        <v>-0.789</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1069</v>
+        <v>-0.1091</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.987</v>
+        <v>-0.9834000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.773</v>
+        <v>-0.789</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.773</v>
+        <v>-0.789</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.773</v>
+        <v>-0.789</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.773</v>
+        <v>-0.789</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.773</v>
+        <v>-0.789</v>
       </c>
       <c r="N38" t="n">
         <v>82</v>
@@ -2198,31 +2198,31 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8944</v>
+        <v>-0.8621</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1237</v>
+        <v>-0.1193</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0418</v>
+        <v>-1.0166</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8944</v>
+        <v>-0.8621</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.487</v>
+        <v>-0.4191</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.4074</v>
+        <v>-0.443</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.487</v>
+        <v>-0.4191</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2532</v>
+        <v>-0.2263</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.4074</v>
+        <v>-0.443</v>
       </c>
       <c r="K39" t="n">
         <v>80</v>
@@ -2231,7 +2231,7 @@
         <v>46</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.6606</v>
+        <v>-0.6693</v>
       </c>
       <c r="N39" t="n">
         <v>126</v>
@@ -2240,93 +2240,93 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.7947</v>
+        <v>-1.568</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2483</v>
+        <v>-0.2169</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.4482</v>
+        <v>-1.338</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.7947</v>
+        <v>-1.568</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.784</v>
+        <v>-2.0321</v>
       </c>
       <c r="G40" t="n">
-        <v>-0.0107</v>
+        <v>0.4641</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.784</v>
+        <v>-2.0321</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.9276</v>
+        <v>-1.0973</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.0107</v>
+        <v>0.4641</v>
       </c>
       <c r="K40" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L40" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.9383</v>
+        <v>-0.6332</v>
       </c>
       <c r="N40" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.8704</v>
+        <v>-1.572</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2587</v>
+        <v>-0.2175</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.4824</v>
+        <v>-1.3398</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.8704</v>
+        <v>-1.572</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.3058</v>
+        <v>-1.6167</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4354</v>
+        <v>0.0447</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.3058</v>
+        <v>-1.6167</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1989</v>
+        <v>-0.873</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4354</v>
+        <v>0.0447</v>
       </c>
       <c r="K41" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L41" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.7635000000000001</v>
+        <v>-0.8283</v>
       </c>
       <c r="N41" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0823</v>
+        <v>-0.1067</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.8106</v>
+        <v>-2.3474</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0823</v>
+        <v>-0.1067</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.8106</v>
+        <v>-2.3474</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.65</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.34</v>
+        <v>-0.3593</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.48</v>
+        <v>-7.9046</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.57</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.4142</v>
+        <v>-0.43</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.112399999999999</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5829</v>
+        <v>-0.5876</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.8238</v>
+        <v>-12.9272</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1172</v>
+        <v>1.1142</v>
       </c>
       <c r="J7" t="n">
-        <v>24.5784</v>
+        <v>24.5124</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0001</v>
+        <v>0.9532</v>
       </c>
       <c r="J8" t="n">
-        <v>22.0022</v>
+        <v>20.9704</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.39</v>
       </c>
       <c r="I9" t="n">
-        <v>0.9489</v>
+        <v>0.8994</v>
       </c>
       <c r="J9" t="n">
-        <v>20.8758</v>
+        <v>19.7868</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8461</v>
+        <v>0.8065</v>
       </c>
       <c r="J10" t="n">
-        <v>18.6142</v>
+        <v>17.743</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7575</v>
+        <v>0.7284</v>
       </c>
       <c r="J11" t="n">
-        <v>16.665</v>
+        <v>16.0248</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5759</v>
+        <v>0.5547</v>
       </c>
       <c r="J12" t="n">
-        <v>20.1565</v>
+        <v>19.4145</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2674</v>
+        <v>0.2677</v>
       </c>
       <c r="J13" t="n">
-        <v>9.359</v>
+        <v>9.3695</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2102</v>
+        <v>-0.2257</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.357</v>
+        <v>-7.8995</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2304</v>
+        <v>-0.2457</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.064</v>
+        <v>-8.599500000000001</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.66</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3655</v>
+        <v>-0.3775</v>
       </c>
       <c r="J16" t="n">
-        <v>-12.7925</v>
+        <v>-13.2125</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1413</v>
+        <v>1.1395</v>
       </c>
       <c r="J17" t="n">
-        <v>39.9455</v>
+        <v>39.8825</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5835</v>
+        <v>0.5663</v>
       </c>
       <c r="J18" t="n">
-        <v>20.4225</v>
+        <v>19.8205</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.19</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5366</v>
+        <v>0.5239</v>
       </c>
       <c r="J19" t="n">
-        <v>18.781</v>
+        <v>18.3365</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.13</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3847</v>
+        <v>0.3858</v>
       </c>
       <c r="J20" t="n">
-        <v>13.4645</v>
+        <v>13.503</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.182</v>
+        <v>-0.1715</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.37</v>
+        <v>-6.0025</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7741</v>
+        <v>0.8939</v>
       </c>
       <c r="J22" t="n">
-        <v>14.7079</v>
+        <v>16.9841</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.62</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5515</v>
+        <v>0.6371</v>
       </c>
       <c r="J23" t="n">
-        <v>10.4785</v>
+        <v>12.1049</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.27</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3329</v>
+        <v>0.3591</v>
       </c>
       <c r="J24" t="n">
-        <v>6.3251</v>
+        <v>6.8229</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3329</v>
+        <v>0.3591</v>
       </c>
       <c r="J25" t="n">
-        <v>6.3251</v>
+        <v>6.8229</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.26</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3233</v>
+        <v>0.3477</v>
       </c>
       <c r="J26" t="n">
-        <v>6.1427</v>
+        <v>6.6063</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0806</v>
+        <v>0.0482</v>
       </c>
       <c r="J27" t="n">
-        <v>1.5314</v>
+        <v>0.9157999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0194</v>
+        <v>-0.0454</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.3686</v>
+        <v>-0.8626</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1655</v>
+        <v>-0.1911</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.1445</v>
+        <v>-3.6309</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.29</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6726</v>
+        <v>-0.6708</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.7794</v>
+        <v>-12.7452</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7482</v>
+        <v>-0.7399</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.2158</v>
+        <v>-14.0581</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.595</v>
+        <v>0.656</v>
       </c>
       <c r="J32" t="n">
-        <v>12.495</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.98</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.024</v>
+        <v>-0.0335</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.504</v>
+        <v>-0.7035</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.73</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.2936</v>
+        <v>-0.3088</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.1656</v>
+        <v>-6.4848</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.2936</v>
+        <v>-0.3088</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.1656</v>
+        <v>-6.4848</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.63</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.3884</v>
+        <v>-0.4003</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.1564</v>
+        <v>-8.4063</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.61</v>
       </c>
       <c r="I37" t="n">
-        <v>0.9801</v>
+        <v>1.0818</v>
       </c>
       <c r="J37" t="n">
-        <v>20.5821</v>
+        <v>22.7178</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.44</v>
       </c>
       <c r="I38" t="n">
-        <v>0.7698</v>
+        <v>0.8556</v>
       </c>
       <c r="J38" t="n">
-        <v>16.1658</v>
+        <v>17.9676</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7066</v>
+        <v>0.7867</v>
       </c>
       <c r="J39" t="n">
-        <v>14.8386</v>
+        <v>16.5207</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2772</v>
+        <v>0.2926</v>
       </c>
       <c r="J40" t="n">
-        <v>5.8212</v>
+        <v>6.1446</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0747</v>
+        <v>-0.0518</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.5687</v>
+        <v>-1.0878</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.36</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5844</v>
+        <v>0.6462</v>
       </c>
       <c r="J42" t="n">
-        <v>15.7788</v>
+        <v>17.4474</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.95</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-0.0809</v>
       </c>
       <c r="J43" t="n">
-        <v>-1.863</v>
+        <v>-2.1843</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.249</v>
+        <v>-0.2643</v>
       </c>
       <c r="J44" t="n">
-        <v>-6.723</v>
+        <v>-7.1361</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2686</v>
+        <v>-0.2836</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.2522</v>
+        <v>-7.6572</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.74</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.2881</v>
+        <v>-0.3027</v>
       </c>
       <c r="J46" t="n">
-        <v>-7.7787</v>
+        <v>-8.1729</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.58</v>
       </c>
       <c r="I47" t="n">
-        <v>0.9693000000000001</v>
+        <v>1.0655</v>
       </c>
       <c r="J47" t="n">
-        <v>26.1711</v>
+        <v>28.7685</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.48</v>
       </c>
       <c r="I48" t="n">
-        <v>0.842</v>
+        <v>0.9293</v>
       </c>
       <c r="J48" t="n">
-        <v>22.734</v>
+        <v>25.0911</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1041</v>
       </c>
       <c r="J49" t="n">
-        <v>2.2815</v>
+        <v>2.8107</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.1036</v>
+        <v>-0.0934</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.7972</v>
+        <v>-2.5218</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3444</v>
+        <v>-0.3255</v>
       </c>
       <c r="J51" t="n">
-        <v>-9.2988</v>
+        <v>-8.788500000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.59</v>
       </c>
       <c r="I52" t="n">
-        <v>0.9524</v>
+        <v>1.0529</v>
       </c>
       <c r="J52" t="n">
-        <v>21.9052</v>
+        <v>24.2167</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>0.7673</v>
+        <v>0.8535</v>
       </c>
       <c r="J53" t="n">
-        <v>17.6479</v>
+        <v>19.6305</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.4</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7171</v>
+        <v>0.7987</v>
       </c>
       <c r="J54" t="n">
-        <v>16.4933</v>
+        <v>18.3701</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.4961</v>
+        <v>0.5535</v>
       </c>
       <c r="J55" t="n">
-        <v>11.4103</v>
+        <v>12.7305</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2465</v>
+        <v>-0.2261</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.6695</v>
+        <v>-5.2003</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4996</v>
+        <v>0.5413</v>
       </c>
       <c r="J57" t="n">
-        <v>11.4908</v>
+        <v>12.4499</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.85</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1645</v>
+        <v>-0.1835</v>
       </c>
       <c r="J58" t="n">
-        <v>-3.7835</v>
+        <v>-4.2205</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2333</v>
+        <v>-0.2522</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.3659</v>
+        <v>-5.8006</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3469</v>
+        <v>-0.3629</v>
       </c>
       <c r="J60" t="n">
-        <v>-7.9787</v>
+        <v>-8.3467</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.42</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5695</v>
+        <v>-0.5732</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.0985</v>
+        <v>-13.1836</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.13</v>
       </c>
       <c r="I62" t="n">
-        <v>1.5918</v>
+        <v>1.723</v>
       </c>
       <c r="J62" t="n">
-        <v>36.6114</v>
+        <v>39.629</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.52</v>
       </c>
       <c r="I63" t="n">
-        <v>0.87</v>
+        <v>0.9638</v>
       </c>
       <c r="J63" t="n">
-        <v>20.01</v>
+        <v>22.1674</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.07</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1896</v>
+        <v>0.2111</v>
       </c>
       <c r="J64" t="n">
-        <v>4.3608</v>
+        <v>4.8553</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1291</v>
+        <v>-0.1113</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.9693</v>
+        <v>-2.5599</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.647</v>
+        <v>-0.5958</v>
       </c>
       <c r="J66" t="n">
-        <v>-14.881</v>
+        <v>-13.7034</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0772</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.4766</v>
+        <v>-1.7756</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0772</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.4766</v>
+        <v>-1.7756</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.95</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.0772</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.4766</v>
+        <v>-1.7756</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.85</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1741</v>
+        <v>-0.1908</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.0043</v>
+        <v>-4.3884</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.7</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3216</v>
+        <v>-0.3362</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.3968</v>
+        <v>-7.7326</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.7040999999999999</v>
+        <v>0.6758999999999999</v>
       </c>
       <c r="J72" t="n">
-        <v>18.3066</v>
+        <v>17.5734</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2469</v>
+        <v>0.2528</v>
       </c>
       <c r="J73" t="n">
-        <v>6.4194</v>
+        <v>6.5728</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2263</v>
+        <v>0.233</v>
       </c>
       <c r="J74" t="n">
-        <v>5.8838</v>
+        <v>6.058</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.83</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.2084</v>
+        <v>-0.222</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.4184</v>
+        <v>-5.772</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.62</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4107</v>
+        <v>-0.4195</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.6782</v>
+        <v>-10.907</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.46</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0909</v>
+        <v>1.0486</v>
       </c>
       <c r="J77" t="n">
-        <v>28.3634</v>
+        <v>27.2636</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8862</v>
+        <v>0.8339</v>
       </c>
       <c r="J78" t="n">
-        <v>23.0412</v>
+        <v>21.6814</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.27</v>
       </c>
       <c r="I79" t="n">
-        <v>0.7251</v>
+        <v>0.6925</v>
       </c>
       <c r="J79" t="n">
-        <v>18.8526</v>
+        <v>18.005</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.1048</v>
       </c>
       <c r="J80" t="n">
-        <v>2.223</v>
+        <v>2.7248</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4595</v>
+        <v>-0.4316</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.947</v>
+        <v>-11.2216</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7798</v>
+        <v>0.7374000000000001</v>
       </c>
       <c r="J82" t="n">
-        <v>19.495</v>
+        <v>18.435</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0277</v>
+        <v>-0.0364</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.6925</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1251</v>
+        <v>-0.1399</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.1275</v>
+        <v>-3.4975</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.68</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3447</v>
+        <v>-0.3578</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.6175</v>
+        <v>-8.945</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.63</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.3916</v>
+        <v>-0.4029</v>
       </c>
       <c r="J86" t="n">
-        <v>-9.789999999999999</v>
+        <v>-10.0725</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>1.09</v>
+        <v>1.0478</v>
       </c>
       <c r="J87" t="n">
-        <v>27.25</v>
+        <v>26.195</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.9497</v>
+        <v>0.892</v>
       </c>
       <c r="J88" t="n">
-        <v>23.7425</v>
+        <v>22.3</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2149</v>
+        <v>0.2287</v>
       </c>
       <c r="J89" t="n">
-        <v>5.3725</v>
+        <v>5.7175</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2149</v>
+        <v>0.2287</v>
       </c>
       <c r="J90" t="n">
-        <v>5.3725</v>
+        <v>5.7175</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.03</v>
       </c>
       <c r="I91" t="n">
-        <v>0.08450000000000001</v>
+        <v>0.1041</v>
       </c>
       <c r="J91" t="n">
-        <v>2.1125</v>
+        <v>2.6025</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.06</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1886</v>
+        <v>0.1896</v>
       </c>
       <c r="J92" t="n">
-        <v>4.715</v>
+        <v>4.74</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.01</v>
       </c>
       <c r="I93" t="n">
-        <v>0.0594</v>
+        <v>0.059</v>
       </c>
       <c r="J93" t="n">
-        <v>1.485</v>
+        <v>1.475</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0264</v>
+        <v>-0.0354</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.66</v>
+        <v>-0.885</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2469</v>
+        <v>-0.2627</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.1725</v>
+        <v>-6.5675</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.68</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3434</v>
+        <v>-0.3568</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.585000000000001</v>
+        <v>-8.92</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.03</v>
       </c>
       <c r="I97" t="n">
-        <v>1.7598</v>
+        <v>1.7595</v>
       </c>
       <c r="J97" t="n">
-        <v>43.995</v>
+        <v>43.9875</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.6874</v>
+        <v>0.662</v>
       </c>
       <c r="J98" t="n">
-        <v>17.185</v>
+        <v>16.55</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3932</v>
+        <v>0.3975</v>
       </c>
       <c r="J99" t="n">
-        <v>9.83</v>
+        <v>9.9375</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1648</v>
+        <v>0.1862</v>
       </c>
       <c r="J100" t="n">
-        <v>4.12</v>
+        <v>4.655</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3934</v>
+        <v>-0.3667</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.835000000000001</v>
+        <v>-9.1675</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.66</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3524</v>
+        <v>1.3273</v>
       </c>
       <c r="J102" t="n">
-        <v>40.572</v>
+        <v>39.819</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.47</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1102</v>
+        <v>1.069</v>
       </c>
       <c r="J103" t="n">
-        <v>33.306</v>
+        <v>32.07</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2811</v>
+        <v>0.2887</v>
       </c>
       <c r="J104" t="n">
-        <v>8.433</v>
+        <v>8.661</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2094</v>
+        <v>-0.2</v>
       </c>
       <c r="J105" t="n">
-        <v>-6.282</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.67</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9902</v>
+        <v>-0.9031</v>
       </c>
       <c r="J106" t="n">
-        <v>-29.706</v>
+        <v>-27.093</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2204</v>
+        <v>0.2236</v>
       </c>
       <c r="J107" t="n">
-        <v>6.612</v>
+        <v>6.708</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0314</v>
+        <v>-0.0393</v>
       </c>
       <c r="J108" t="n">
-        <v>-0.9419999999999999</v>
+        <v>-1.179</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.083</v>
+        <v>-0.0951</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.49</v>
+        <v>-2.853</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.92</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1058</v>
+        <v>-0.1191</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.174</v>
+        <v>-3.573</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.79</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.242</v>
+        <v>-0.2569</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.26</v>
+        <v>-7.707</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.36</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7689</v>
+        <v>0.7266</v>
       </c>
       <c r="J112" t="n">
-        <v>17.6847</v>
+        <v>16.7118</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1417</v>
+        <v>0.1432</v>
       </c>
       <c r="J113" t="n">
-        <v>3.2591</v>
+        <v>3.2936</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.85</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1763</v>
+        <v>-0.1925</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.0549</v>
+        <v>-4.4275</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.73</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.2954</v>
+        <v>-0.3103</v>
       </c>
       <c r="J115" t="n">
-        <v>-6.7942</v>
+        <v>-7.1369</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.52</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4913</v>
+        <v>-0.4979</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.2999</v>
+        <v>-11.4517</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>1.2269</v>
+        <v>1.1986</v>
       </c>
       <c r="J117" t="n">
-        <v>28.2187</v>
+        <v>27.5678</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.5</v>
       </c>
       <c r="I118" t="n">
-        <v>1.1271</v>
+        <v>1.0916</v>
       </c>
       <c r="J118" t="n">
-        <v>25.9233</v>
+        <v>25.1068</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.5809</v>
       </c>
       <c r="J119" t="n">
-        <v>13.7379</v>
+        <v>13.3607</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.0688</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="J120" t="n">
-        <v>1.5824</v>
+        <v>2.1436</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1193</v>
+        <v>-0.1044</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.7439</v>
+        <v>-2.4012</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.11</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2822</v>
+        <v>0.2832</v>
       </c>
       <c r="J122" t="n">
-        <v>10.1592</v>
+        <v>10.1952</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.077</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="J123" t="n">
-        <v>2.772</v>
+        <v>2.9232</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1284</v>
+        <v>-0.1424</v>
       </c>
       <c r="J124" t="n">
-        <v>-4.6224</v>
+        <v>-5.1264</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.87</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1607</v>
+        <v>-0.1754</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.7852</v>
+        <v>-6.3144</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2022</v>
+        <v>-0.2172</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.2792</v>
+        <v>-7.8192</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0877</v>
+        <v>1.0428</v>
       </c>
       <c r="J127" t="n">
-        <v>39.1572</v>
+        <v>37.5408</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4942</v>
+        <v>0.4839</v>
       </c>
       <c r="J128" t="n">
-        <v>17.7912</v>
+        <v>17.4204</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.11</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3403</v>
+        <v>0.3427</v>
       </c>
       <c r="J129" t="n">
-        <v>12.2508</v>
+        <v>12.3372</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.1632</v>
+        <v>0.177</v>
       </c>
       <c r="J130" t="n">
-        <v>5.8752</v>
+        <v>6.372</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0374</v>
+        <v>-0.0257</v>
       </c>
       <c r="J131" t="n">
-        <v>-1.3464</v>
+        <v>-0.9252</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0738</v>
+        <v>1.0209</v>
       </c>
       <c r="J132" t="n">
-        <v>38.6568</v>
+        <v>36.7524</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.11</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3576</v>
+        <v>0.3545</v>
       </c>
       <c r="J133" t="n">
-        <v>12.8736</v>
+        <v>12.762</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1092</v>
+        <v>-0.1102</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.9312</v>
+        <v>-3.9672</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1463</v>
+        <v>-0.1466</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.2668</v>
+        <v>-5.2776</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5342</v>
+        <v>-0.5063</v>
       </c>
       <c r="J136" t="n">
-        <v>-19.2312</v>
+        <v>-18.2268</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0822</v>
+        <v>1.0518</v>
       </c>
       <c r="J137" t="n">
-        <v>38.9592</v>
+        <v>37.8648</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3924</v>
+        <v>0.3963</v>
       </c>
       <c r="J138" t="n">
-        <v>14.1264</v>
+        <v>14.2668</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.1878</v>
+        <v>0.2002</v>
       </c>
       <c r="J139" t="n">
-        <v>6.7608</v>
+        <v>7.2072</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.06</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1456</v>
+        <v>0.1587</v>
       </c>
       <c r="J140" t="n">
-        <v>5.2416</v>
+        <v>5.7132</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4753</v>
+        <v>-0.4796</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.1108</v>
+        <v>-17.2656</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.23</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8338</v>
+        <v>1.9372</v>
       </c>
       <c r="J142" t="n">
-        <v>38.5098</v>
+        <v>40.6812</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1497</v>
+        <v>1.1214</v>
       </c>
       <c r="J143" t="n">
-        <v>24.1437</v>
+        <v>23.5494</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6604</v>
+        <v>0.6435</v>
       </c>
       <c r="J144" t="n">
-        <v>13.8684</v>
+        <v>13.5135</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2528</v>
+        <v>0.2756</v>
       </c>
       <c r="J145" t="n">
-        <v>5.3088</v>
+        <v>5.7876</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2666</v>
+        <v>-0.2402</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.5986</v>
+        <v>-5.0442</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.96</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0296</v>
+        <v>-0.0465</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.6216</v>
+        <v>-0.9765</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.82</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1925</v>
+        <v>-0.2121</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.0425</v>
+        <v>-4.4541</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2222</v>
+        <v>-0.2416</v>
       </c>
       <c r="J149" t="n">
-        <v>-4.6662</v>
+        <v>-5.0736</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.67</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3345</v>
+        <v>-0.3516</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.0245</v>
+        <v>-7.3836</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.3909</v>
+        <v>-0.4055</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.2089</v>
+        <v>-8.515499999999999</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.66</v>
       </c>
       <c r="I152" t="n">
-        <v>1.1276</v>
+        <v>1.0966</v>
       </c>
       <c r="J152" t="n">
-        <v>32.7004</v>
+        <v>31.8014</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.03</v>
       </c>
       <c r="I153" t="n">
-        <v>0.0936</v>
+        <v>0.1013</v>
       </c>
       <c r="J153" t="n">
-        <v>2.7144</v>
+        <v>2.9377</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.99</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.02</v>
+        <v>-0.0248</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.58</v>
+        <v>-0.7192</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2378</v>
+        <v>-0.2515</v>
       </c>
       <c r="J155" t="n">
-        <v>-6.8962</v>
+        <v>-7.2935</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.47</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5451</v>
+        <v>-0.5474</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.8079</v>
+        <v>-15.8746</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>1.3195</v>
+        <v>1.283</v>
       </c>
       <c r="J157" t="n">
-        <v>38.2655</v>
+        <v>37.207</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.1</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3428</v>
+        <v>0.3378</v>
       </c>
       <c r="J158" t="n">
-        <v>9.9412</v>
+        <v>9.796200000000001</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.07</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2546</v>
+        <v>0.2558</v>
       </c>
       <c r="J159" t="n">
-        <v>7.3834</v>
+        <v>7.4182</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.928</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="J160" t="n">
-        <v>-26.912</v>
+        <v>-24.8037</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-1.0007</v>
+        <v>-0.9181</v>
       </c>
       <c r="J161" t="n">
-        <v>-29.0203</v>
+        <v>-26.6249</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3498</v>
+        <v>1.3334</v>
       </c>
       <c r="J162" t="n">
-        <v>32.3952</v>
+        <v>32.0016</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.1214</v>
+        <v>1.0891</v>
       </c>
       <c r="J163" t="n">
-        <v>26.9136</v>
+        <v>26.1384</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.913</v>
+        <v>0.865</v>
       </c>
       <c r="J164" t="n">
-        <v>21.912</v>
+        <v>20.76</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4524</v>
+        <v>0.4552</v>
       </c>
       <c r="J165" t="n">
-        <v>10.8576</v>
+        <v>10.9248</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.07</v>
       </c>
       <c r="I166" t="n">
-        <v>0.1765</v>
+        <v>0.2019</v>
       </c>
       <c r="J166" t="n">
-        <v>4.236</v>
+        <v>4.8456</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.96</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0325</v>
+        <v>-0.0488</v>
       </c>
       <c r="J167" t="n">
-        <v>-0.78</v>
+        <v>-1.1712</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1193</v>
+        <v>-0.1383</v>
       </c>
       <c r="J168" t="n">
-        <v>-2.8632</v>
+        <v>-3.3192</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.83</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1841</v>
+        <v>-0.2033</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.4184</v>
+        <v>-4.8792</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3552</v>
+        <v>-0.3711</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.524800000000001</v>
+        <v>-8.9064</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.58</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4208</v>
+        <v>-0.4336</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.0992</v>
+        <v>-10.4064</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3165/event_3165_evp_summary.xlsx
+++ b/database/event/3165/event_3165_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.3618</v>
+        <v>5.4166</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7417</v>
+        <v>0.7493</v>
       </c>
       <c r="D2" t="n">
-        <v>1.8166</v>
+        <v>1.8617</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3618</v>
+        <v>5.4166</v>
       </c>
       <c r="F2" t="n">
-        <v>1.275</v>
+        <v>1.3187</v>
       </c>
       <c r="G2" t="n">
-        <v>4.0868</v>
+        <v>4.0979</v>
       </c>
       <c r="H2" t="n">
-        <v>1.275</v>
+        <v>1.3187</v>
       </c>
       <c r="I2" t="n">
-        <v>0.6885</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>4.0868</v>
+        <v>4.0979</v>
       </c>
       <c r="K2" t="n">
         <v>76</v>
@@ -529,7 +529,7 @@
         <v>124</v>
       </c>
       <c r="M2" t="n">
-        <v>4.775300000000001</v>
+        <v>4.8383</v>
       </c>
       <c r="N2" t="n">
         <v>200</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.227</v>
+        <v>5.1513</v>
       </c>
       <c r="C3" t="n">
-        <v>0.723</v>
+        <v>0.7126</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7552</v>
+        <v>1.7409</v>
       </c>
       <c r="E3" t="n">
-        <v>5.227</v>
+        <v>5.1513</v>
       </c>
       <c r="F3" t="n">
-        <v>3.044</v>
+        <v>3.0646</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1831</v>
+        <v>2.0867</v>
       </c>
       <c r="H3" t="n">
-        <v>5.149</v>
+        <v>5.0631</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7804</v>
+        <v>2.8428</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1831</v>
+        <v>2.0867</v>
       </c>
       <c r="K3" t="n">
         <v>61</v>
@@ -575,7 +575,7 @@
         <v>67</v>
       </c>
       <c r="M3" t="n">
-        <v>4.9635</v>
+        <v>4.9295</v>
       </c>
       <c r="N3" t="n">
         <v>128</v>
@@ -584,93 +584,93 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>tarik</t>
+          <t>NAF</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.0501</v>
+        <v>5.0147</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6986</v>
+        <v>0.6937</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6747</v>
+        <v>1.6786</v>
       </c>
       <c r="E4" t="n">
-        <v>5.0501</v>
+        <v>5.0147</v>
       </c>
       <c r="F4" t="n">
-        <v>2.739</v>
+        <v>2.8695</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3111</v>
+        <v>2.1452</v>
       </c>
       <c r="H4" t="n">
-        <v>4.1427</v>
+        <v>4.3308</v>
       </c>
       <c r="I4" t="n">
-        <v>2.237</v>
+        <v>2.4316</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3111</v>
+        <v>2.1452</v>
       </c>
       <c r="K4" t="n">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="L4" t="n">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="M4" t="n">
-        <v>4.5481</v>
+        <v>4.5768</v>
       </c>
       <c r="N4" t="n">
-        <v>200</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>NAF</t>
+          <t>tarik</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.0423</v>
+        <v>5.0094</v>
       </c>
       <c r="C5" t="n">
-        <v>0.6975</v>
+        <v>0.6929</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6712</v>
+        <v>1.6762</v>
       </c>
       <c r="E5" t="n">
-        <v>5.0423</v>
+        <v>5.0094</v>
       </c>
       <c r="F5" t="n">
-        <v>2.8318</v>
+        <v>2.7551</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2105</v>
+        <v>2.2543</v>
       </c>
       <c r="H5" t="n">
-        <v>4.449</v>
+        <v>3.9014</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4024</v>
+        <v>2.1905</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2105</v>
+        <v>2.2543</v>
       </c>
       <c r="K5" t="n">
-        <v>54</v>
+        <v>76</v>
       </c>
       <c r="L5" t="n">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6129</v>
+        <v>4.444800000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>157</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6">
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.7592</v>
+        <v>4.8461</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6583</v>
+        <v>0.6703</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5423</v>
+        <v>1.6018</v>
       </c>
       <c r="E6" t="n">
-        <v>4.7592</v>
+        <v>4.8461</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4848</v>
+        <v>2.5834</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2744</v>
+        <v>2.2627</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3041</v>
+        <v>3.2565</v>
       </c>
       <c r="I6" t="n">
-        <v>1.7842</v>
+        <v>1.8284</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2744</v>
+        <v>2.2627</v>
       </c>
       <c r="K6" t="n">
         <v>76</v>
@@ -713,7 +713,7 @@
         <v>124</v>
       </c>
       <c r="M6" t="n">
-        <v>4.0586</v>
+        <v>4.0911</v>
       </c>
       <c r="N6" t="n">
         <v>200</v>
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.389</v>
+        <v>3.4677</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4688</v>
+        <v>0.4797</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9185</v>
+        <v>0.9739</v>
       </c>
       <c r="E7" t="n">
-        <v>3.389</v>
+        <v>3.4677</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6465</v>
+        <v>1.6679</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7425</v>
+        <v>1.7997</v>
       </c>
       <c r="H7" t="n">
-        <v>1.6465</v>
+        <v>1.6679</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8891</v>
+        <v>0.9365</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7425</v>
+        <v>1.7997</v>
       </c>
       <c r="K7" t="n">
         <v>54</v>
@@ -759,7 +759,7 @@
         <v>103</v>
       </c>
       <c r="M7" t="n">
-        <v>2.6316</v>
+        <v>2.7362</v>
       </c>
       <c r="N7" t="n">
         <v>157</v>
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.4804</v>
+        <v>2.5721</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3431</v>
+        <v>0.3558</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5049</v>
+        <v>0.5659</v>
       </c>
       <c r="E8" t="n">
-        <v>2.4804</v>
+        <v>2.5721</v>
       </c>
       <c r="F8" t="n">
-        <v>2.7139</v>
+        <v>2.761</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2335</v>
+        <v>-0.1889</v>
       </c>
       <c r="H8" t="n">
-        <v>4.0599</v>
+        <v>3.9235</v>
       </c>
       <c r="I8" t="n">
-        <v>2.1923</v>
+        <v>2.2029</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.2335</v>
+        <v>-0.1889</v>
       </c>
       <c r="K8" t="n">
         <v>54</v>
@@ -805,7 +805,7 @@
         <v>103</v>
       </c>
       <c r="M8" t="n">
-        <v>1.9588</v>
+        <v>2.014</v>
       </c>
       <c r="N8" t="n">
         <v>157</v>
@@ -814,185 +814,185 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Skadoodle</t>
+          <t>mixwell</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.9619</v>
+        <v>2.0024</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2714</v>
+        <v>0.277</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2689</v>
+        <v>0.3064</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9619</v>
+        <v>2.0024</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5424</v>
+        <v>2.6712</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4195</v>
+        <v>-0.6688</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5424</v>
+        <v>3.5863</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8329</v>
+        <v>2.0136</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4195</v>
+        <v>-0.6688</v>
       </c>
       <c r="K9" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="L9" t="n">
-        <v>124</v>
+        <v>46</v>
       </c>
       <c r="M9" t="n">
-        <v>1.2524</v>
+        <v>1.3448</v>
       </c>
       <c r="N9" t="n">
-        <v>200</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>mixwell</t>
+          <t>SicK</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1.9262</v>
+        <v>1.7575</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2664</v>
+        <v>0.2431</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2526</v>
+        <v>0.1948</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9262</v>
+        <v>1.7575</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6253</v>
+        <v>1.7575</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>3.7677</v>
+        <v>1.7575</v>
       </c>
       <c r="I10" t="n">
-        <v>2.0345</v>
+        <v>1.7575</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="L10" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>1.3354</v>
+        <v>1.7575</v>
       </c>
       <c r="N10" t="n">
-        <v>126</v>
+        <v>85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SicK</t>
+          <t>Rickeh</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.8477</v>
+        <v>1.754</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2556</v>
+        <v>0.2426</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2169</v>
+        <v>0.1932</v>
       </c>
       <c r="E11" t="n">
-        <v>1.8477</v>
+        <v>1.754</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8477</v>
+        <v>1.754</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>1.8477</v>
+        <v>1.754</v>
       </c>
       <c r="I11" t="n">
-        <v>1.8477</v>
+        <v>1.754</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.8477</v>
+        <v>1.754</v>
       </c>
       <c r="N11" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Rickeh</t>
+          <t>Skadoodle</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.8232</v>
+        <v>1.7443</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2522</v>
+        <v>0.2413</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2058</v>
+        <v>0.1888</v>
       </c>
       <c r="E12" t="n">
-        <v>1.8232</v>
+        <v>1.7443</v>
       </c>
       <c r="F12" t="n">
-        <v>1.8232</v>
+        <v>1.4052</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.3391</v>
       </c>
       <c r="H12" t="n">
-        <v>1.8232</v>
+        <v>1.4052</v>
       </c>
       <c r="I12" t="n">
-        <v>1.8232</v>
+        <v>0.789</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.3391</v>
       </c>
       <c r="K12" t="n">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>124</v>
       </c>
       <c r="M12" t="n">
-        <v>1.8232</v>
+        <v>1.1281</v>
       </c>
       <c r="N12" t="n">
-        <v>52</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.6576</v>
+        <v>1.5271</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2293</v>
+        <v>0.2112</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1304</v>
+        <v>0.08989999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6576</v>
+        <v>1.5271</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7578</v>
+        <v>0.6456</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8998</v>
+        <v>0.8815</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7578</v>
+        <v>0.6456</v>
       </c>
       <c r="I13" t="n">
-        <v>0.4092</v>
+        <v>0.3625</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8998</v>
+        <v>0.8815</v>
       </c>
       <c r="K13" t="n">
         <v>76</v>
@@ -1035,7 +1035,7 @@
         <v>124</v>
       </c>
       <c r="M13" t="n">
-        <v>1.309</v>
+        <v>1.244</v>
       </c>
       <c r="N13" t="n">
         <v>200</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.6186</v>
+        <v>1.4102</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2239</v>
+        <v>0.1951</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1126</v>
+        <v>0.0366</v>
       </c>
       <c r="E14" t="n">
-        <v>1.6186</v>
+        <v>1.4102</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8824</v>
+        <v>1.6911</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.2638</v>
+        <v>-0.2809</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8824</v>
+        <v>1.6911</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0165</v>
+        <v>0.9495</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2638</v>
+        <v>-0.2809</v>
       </c>
       <c r="K14" t="n">
         <v>61</v>
@@ -1081,7 +1081,7 @@
         <v>67</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7526999999999999</v>
+        <v>0.6686000000000001</v>
       </c>
       <c r="N14" t="n">
         <v>128</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4286</v>
+        <v>1.3934</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1976</v>
+        <v>0.1927</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0261</v>
+        <v>0.029</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4286</v>
+        <v>1.3934</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4286</v>
+        <v>1.3934</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4286</v>
+        <v>1.3934</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4286</v>
+        <v>1.3934</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.4286</v>
+        <v>1.3934</v>
       </c>
       <c r="N15" t="n">
         <v>82</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2708</v>
+        <v>1.1689</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1758</v>
+        <v>0.1617</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0457</v>
+        <v>-0.0733</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2708</v>
+        <v>1.1689</v>
       </c>
       <c r="F16" t="n">
-        <v>1.5315</v>
+        <v>1.4006</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.2607</v>
+        <v>-0.2317</v>
       </c>
       <c r="H16" t="n">
-        <v>1.5315</v>
+        <v>1.4006</v>
       </c>
       <c r="I16" t="n">
-        <v>0.827</v>
+        <v>0.7864</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.2607</v>
+        <v>-0.2317</v>
       </c>
       <c r="K16" t="n">
         <v>80</v>
@@ -1173,7 +1173,7 @@
         <v>46</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5663</v>
+        <v>0.5547</v>
       </c>
       <c r="N16" t="n">
         <v>126</v>
@@ -1186,28 +1186,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.1804</v>
+        <v>1.1238</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1633</v>
+        <v>0.1555</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.08690000000000001</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1804</v>
+        <v>1.1238</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1804</v>
+        <v>1.1238</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.1804</v>
+        <v>1.1238</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1804</v>
+        <v>1.1238</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.1804</v>
+        <v>1.1238</v>
       </c>
       <c r="N17" t="n">
         <v>85</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8308</v>
+        <v>0.8167</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1149</v>
+        <v>0.113</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.246</v>
+        <v>-0.2337</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8308</v>
+        <v>0.8167</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8308</v>
+        <v>0.8167</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8308</v>
+        <v>0.8167</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8308</v>
+        <v>0.8167</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8308</v>
+        <v>0.8167</v>
       </c>
       <c r="N18" t="n">
         <v>85</v>
@@ -1278,31 +1278,31 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7125</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1074</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.2706</v>
+        <v>-0.2812</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7766999999999999</v>
+        <v>0.7125</v>
       </c>
       <c r="F19" t="n">
-        <v>0.532</v>
+        <v>0.5003</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2447</v>
+        <v>0.2122</v>
       </c>
       <c r="H19" t="n">
-        <v>0.532</v>
+        <v>0.5003</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2873</v>
+        <v>0.2809</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2447</v>
+        <v>0.2122</v>
       </c>
       <c r="K19" t="n">
         <v>61</v>
@@ -1311,7 +1311,7 @@
         <v>67</v>
       </c>
       <c r="M19" t="n">
-        <v>0.532</v>
+        <v>0.4931</v>
       </c>
       <c r="N19" t="n">
         <v>128</v>
@@ -1324,28 +1324,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.5591</v>
+        <v>0.5108</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.0707</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3697</v>
+        <v>-0.3731</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5591</v>
+        <v>0.5108</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5591</v>
+        <v>0.5108</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0.5591</v>
+        <v>0.5108</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5591</v>
+        <v>0.5108</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5591</v>
+        <v>0.5108</v>
       </c>
       <c r="N20" t="n">
         <v>85</v>
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.2895</v>
+        <v>0.2072</v>
       </c>
       <c r="C21" t="n">
-        <v>0.04</v>
+        <v>0.0287</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4924</v>
+        <v>-0.5114</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2895</v>
+        <v>0.2072</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2895</v>
+        <v>0.2072</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2895</v>
+        <v>0.2072</v>
       </c>
       <c r="I21" t="n">
-        <v>0.2895</v>
+        <v>0.2072</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2895</v>
+        <v>0.2072</v>
       </c>
       <c r="N21" t="n">
         <v>85</v>
@@ -1416,28 +1416,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.2344</v>
+        <v>0.1944</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0324</v>
+        <v>0.0269</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5175</v>
+        <v>-0.5172</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2344</v>
+        <v>0.1944</v>
       </c>
       <c r="F22" t="n">
-        <v>0.2344</v>
+        <v>0.1944</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2344</v>
+        <v>0.1944</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2344</v>
+        <v>0.1944</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2344</v>
+        <v>0.1944</v>
       </c>
       <c r="N22" t="n">
         <v>60</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.2233</v>
+        <v>0.1592</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0309</v>
+        <v>0.022</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.5226</v>
+        <v>-0.5333</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2233</v>
+        <v>0.1592</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3776</v>
+        <v>1.2118</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.1543</v>
+        <v>-1.0526</v>
       </c>
       <c r="H23" t="n">
-        <v>1.3776</v>
+        <v>1.2118</v>
       </c>
       <c r="I23" t="n">
-        <v>0.7439</v>
+        <v>0.6804</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1543</v>
+        <v>-1.0526</v>
       </c>
       <c r="K23" t="n">
         <v>54</v>
@@ -1495,7 +1495,7 @@
         <v>103</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.4104000000000001</v>
+        <v>-0.3722</v>
       </c>
       <c r="N23" t="n">
         <v>157</v>
@@ -1508,28 +1508,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.1184</v>
+        <v>0.0905</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0164</v>
+        <v>0.0125</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.5703</v>
+        <v>-0.5646</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1184</v>
+        <v>0.0905</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1184</v>
+        <v>0.0905</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1184</v>
+        <v>0.0905</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1184</v>
+        <v>0.0905</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1184</v>
+        <v>0.0905</v>
       </c>
       <c r="N24" t="n">
         <v>52</v>
@@ -1550,78 +1550,78 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>HS</t>
+          <t>AnJ</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.1037</v>
+        <v>0.0196</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0143</v>
+        <v>0.0027</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.577</v>
+        <v>-0.5969</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1037</v>
+        <v>0.0196</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7541</v>
+        <v>0.0196</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.6504</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7541</v>
+        <v>0.0196</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4072</v>
+        <v>0.0196</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.6504</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L25" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2432</v>
+        <v>0.0196</v>
       </c>
       <c r="N25" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AnJ</t>
+          <t>CeRq</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0345</v>
+        <v>-0.0102</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0048</v>
+        <v>-0.0014</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.6085</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>0.0345</v>
+        <v>-0.0102</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0345</v>
+        <v>-0.0102</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0345</v>
+        <v>-0.0102</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0345</v>
+        <v>-0.0102</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -1633,7 +1633,7 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>0.0345</v>
+        <v>-0.0102</v>
       </c>
       <c r="N26" t="n">
         <v>82</v>
@@ -1642,47 +1642,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CeRq</t>
+          <t>HS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0183</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0013</v>
+        <v>-0.0025</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.6284</v>
+        <v>-0.6141</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.0183</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.6292</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.6475</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.6292</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.3533</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.6475</v>
       </c>
       <c r="K27" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.009299999999999999</v>
+        <v>-0.2942</v>
       </c>
       <c r="N27" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
@@ -1692,28 +1692,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.101</v>
+        <v>-0.1035</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.014</v>
+        <v>-0.0143</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6702</v>
+        <v>-0.6529</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.101</v>
+        <v>-0.1035</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.101</v>
+        <v>-0.1035</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.101</v>
+        <v>-0.1035</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.101</v>
+        <v>-0.1035</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -1725,7 +1725,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.101</v>
+        <v>-0.1035</v>
       </c>
       <c r="N28" t="n">
         <v>82</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.1221</v>
+        <v>-0.1295</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0169</v>
+        <v>-0.0179</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6798</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.1221</v>
+        <v>-0.1295</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.1221</v>
+        <v>-0.1295</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.1221</v>
+        <v>-0.1295</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1221</v>
+        <v>-0.1295</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -1771,7 +1771,7 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1221</v>
+        <v>-0.1295</v>
       </c>
       <c r="N29" t="n">
         <v>60</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.2322</v>
+        <v>-0.2531</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0321</v>
+        <v>-0.035</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.7299</v>
+        <v>-0.7211</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.2322</v>
+        <v>-0.2531</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0733</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3055</v>
+        <v>-0.3284</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0733</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>0.0396</v>
+        <v>0.0423</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3055</v>
+        <v>-0.3284</v>
       </c>
       <c r="K30" t="n">
         <v>61</v>
@@ -1817,7 +1817,7 @@
         <v>67</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.2659</v>
+        <v>-0.2861</v>
       </c>
       <c r="N30" t="n">
         <v>128</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.3137</v>
+        <v>-0.2785</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0434</v>
+        <v>-0.0385</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.767</v>
+        <v>-0.7327</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.3137</v>
+        <v>-0.2785</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.3137</v>
+        <v>-0.2785</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.3137</v>
+        <v>-0.2785</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3137</v>
+        <v>-0.2785</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.3137</v>
+        <v>-0.2785</v>
       </c>
       <c r="N31" t="n">
         <v>60</v>
@@ -1872,93 +1872,93 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>USTILO</t>
+          <t>reltuC</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3544</v>
+        <v>-0.4238</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.049</v>
+        <v>-0.0586</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7855</v>
+        <v>-0.7988</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3544</v>
+        <v>-0.4238</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.2985</v>
+        <v>-0.4238</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9441000000000001</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.2985</v>
+        <v>-0.4238</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.7012</v>
+        <v>-0.4238</v>
       </c>
       <c r="J32" t="n">
-        <v>0.9441000000000001</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L32" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2429</v>
+        <v>-0.4238</v>
       </c>
       <c r="N32" t="n">
-        <v>157</v>
+        <v>52</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>reltuC</t>
+          <t>USTILO</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3966</v>
+        <v>-0.4372</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0549</v>
+        <v>-0.0605</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8047</v>
+        <v>-0.805</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3966</v>
+        <v>-0.4372</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3966</v>
+        <v>-1.2831</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>0.8459</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3966</v>
+        <v>-1.2831</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3966</v>
+        <v>-0.7204</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>0.8459</v>
       </c>
       <c r="K33" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3966</v>
+        <v>0.1254999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>52</v>
+        <v>157</v>
       </c>
     </row>
     <row r="34">
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.5135</v>
+        <v>-0.4812</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.07099999999999999</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.858</v>
+        <v>-0.825</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.5135</v>
+        <v>-0.4812</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.5135</v>
+        <v>-0.4812</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.5135</v>
+        <v>-0.4812</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.5135</v>
+        <v>-0.4812</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.5135</v>
+        <v>-0.4812</v>
       </c>
       <c r="N34" t="n">
         <v>60</v>
@@ -2014,28 +2014,28 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.5618</v>
+        <v>-0.5243</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.0725</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8799</v>
+        <v>-0.8446</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.5618</v>
+        <v>-0.5243</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.5618</v>
+        <v>-0.5243</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.5618</v>
+        <v>-0.5243</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.5618</v>
+        <v>-0.5243</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.5618</v>
+        <v>-0.5243</v>
       </c>
       <c r="N35" t="n">
         <v>52</v>
@@ -2060,28 +2060,28 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.6508</v>
+        <v>-0.6219</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.09</v>
+        <v>-0.08599999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9205</v>
+        <v>-0.8891</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.6508</v>
+        <v>-0.6219</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.6508</v>
+        <v>-0.6219</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.6508</v>
+        <v>-0.6219</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.6508</v>
+        <v>-0.6219</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.6508</v>
+        <v>-0.6219</v>
       </c>
       <c r="N36" t="n">
         <v>60</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.7399</v>
+        <v>-0.7288</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1023</v>
+        <v>-0.1008</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.961</v>
+        <v>-0.9378</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.7399</v>
+        <v>-0.7288</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.7399</v>
+        <v>-0.7288</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.7399</v>
+        <v>-0.7288</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.7399</v>
+        <v>-0.7288</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.7399</v>
+        <v>-0.7288</v>
       </c>
       <c r="N37" t="n">
         <v>52</v>
@@ -2148,185 +2148,185 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>daps</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.789</v>
+        <v>-0.7511</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1091</v>
+        <v>-0.1039</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9834000000000001</v>
+        <v>-0.9479</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.789</v>
+        <v>-0.7511</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.789</v>
+        <v>-0.3443</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>-0.4068</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.789</v>
+        <v>-0.3443</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.789</v>
+        <v>-0.1933</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>-0.4068</v>
       </c>
       <c r="K38" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.789</v>
+        <v>-0.6001</v>
       </c>
       <c r="N38" t="n">
-        <v>82</v>
+        <v>126</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>daps</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-0.8621</v>
+        <v>-0.758</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1193</v>
+        <v>-0.1049</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0166</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.8621</v>
+        <v>-0.758</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.4191</v>
+        <v>-0.758</v>
       </c>
       <c r="G39" t="n">
-        <v>-0.443</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.4191</v>
+        <v>-0.758</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.2263</v>
+        <v>-0.758</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.443</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="L39" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.6693</v>
+        <v>-0.758</v>
       </c>
       <c r="N39" t="n">
-        <v>126</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>allu</t>
+          <t>nitr0</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.568</v>
+        <v>-1.3692</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.2169</v>
+        <v>-0.1894</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.338</v>
+        <v>-1.2295</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.568</v>
+        <v>-1.3692</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.0321</v>
+        <v>-1.4113</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4641</v>
+        <v>0.0421</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.0321</v>
+        <v>-1.4113</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.0973</v>
+        <v>-0.7924</v>
       </c>
       <c r="J40" t="n">
-        <v>0.4641</v>
+        <v>0.0421</v>
       </c>
       <c r="K40" t="n">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="L40" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.6332</v>
+        <v>-0.7503</v>
       </c>
       <c r="N40" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>nitr0</t>
+          <t>allu</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-1.572</v>
+        <v>-1.4564</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2175</v>
+        <v>-0.2015</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.3398</v>
+        <v>-1.2692</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.572</v>
+        <v>-1.4564</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6167</v>
+        <v>-1.9175</v>
       </c>
       <c r="G41" t="n">
-        <v>0.0447</v>
+        <v>0.4611</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.6167</v>
+        <v>-1.9175</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.873</v>
+        <v>-1.0766</v>
       </c>
       <c r="J41" t="n">
-        <v>0.0447</v>
+        <v>0.4611</v>
       </c>
       <c r="K41" t="n">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="L41" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.8283</v>
+        <v>-0.6154999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
@@ -2429,10 +2429,10 @@
         <v>0.9</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1067</v>
+        <v>-0.0898</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.3474</v>
+        <v>-1.9756</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>0.9</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1067</v>
+        <v>-0.0898</v>
       </c>
       <c r="J3" t="n">
-        <v>-2.3474</v>
+        <v>-1.9756</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>0.65</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3593</v>
+        <v>-0.3471</v>
       </c>
       <c r="J4" t="n">
-        <v>-7.9046</v>
+        <v>-7.6362</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>0.57</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.43</v>
+        <v>-0.4215</v>
       </c>
       <c r="J5" t="n">
-        <v>-9.460000000000001</v>
+        <v>-9.273</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>0.39</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5876</v>
+        <v>-0.5981</v>
       </c>
       <c r="J6" t="n">
-        <v>-12.9272</v>
+        <v>-13.1582</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>1.51</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1142</v>
+        <v>1.1232</v>
       </c>
       <c r="J7" t="n">
-        <v>24.5124</v>
+        <v>24.7104</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>1.42</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9532</v>
+        <v>0.9484</v>
       </c>
       <c r="J8" t="n">
-        <v>20.9704</v>
+        <v>20.8648</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>1.39</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8994</v>
+        <v>0.8905999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>19.7868</v>
+        <v>19.5932</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>1.34</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8065</v>
+        <v>0.7917</v>
       </c>
       <c r="J10" t="n">
-        <v>17.743</v>
+        <v>17.4174</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>1.3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7284</v>
+        <v>0.7092000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>16.0248</v>
+        <v>15.6024</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.26</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5547</v>
+        <v>0.4978</v>
       </c>
       <c r="J12" t="n">
-        <v>19.4145</v>
+        <v>17.423</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2677</v>
+        <v>0.2197</v>
       </c>
       <c r="J13" t="n">
-        <v>9.3695</v>
+        <v>7.6895</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>0.82</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.2257</v>
+        <v>-0.2055</v>
       </c>
       <c r="J14" t="n">
-        <v>-7.8995</v>
+        <v>-7.1925</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.8</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2457</v>
+        <v>-0.2258</v>
       </c>
       <c r="J15" t="n">
-        <v>-8.599500000000001</v>
+        <v>-7.903</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.66</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3775</v>
+        <v>-0.3646</v>
       </c>
       <c r="J16" t="n">
-        <v>-13.2125</v>
+        <v>-12.761</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.5</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1395</v>
+        <v>1.1469</v>
       </c>
       <c r="J17" t="n">
-        <v>39.8825</v>
+        <v>40.1415</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>1.21</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5663</v>
+        <v>0.5326</v>
       </c>
       <c r="J18" t="n">
-        <v>19.8205</v>
+        <v>18.641</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>1.19</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5239</v>
+        <v>0.4895</v>
       </c>
       <c r="J19" t="n">
-        <v>18.3365</v>
+        <v>17.1325</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>1.13</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3858</v>
+        <v>0.3516</v>
       </c>
       <c r="J20" t="n">
-        <v>13.503</v>
+        <v>12.306</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.1715</v>
+        <v>-0.1402</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.0025</v>
+        <v>-4.907</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>2.01</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8939</v>
+        <v>0.8373</v>
       </c>
       <c r="J22" t="n">
-        <v>16.9841</v>
+        <v>15.9087</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.62</v>
       </c>
       <c r="I23" t="n">
-        <v>0.6371</v>
+        <v>0.5981</v>
       </c>
       <c r="J23" t="n">
-        <v>12.1049</v>
+        <v>11.3639</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>1.27</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3591</v>
+        <v>0.3056</v>
       </c>
       <c r="J24" t="n">
-        <v>6.8229</v>
+        <v>5.8064</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>1.27</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3591</v>
+        <v>0.3056</v>
       </c>
       <c r="J25" t="n">
-        <v>6.8229</v>
+        <v>5.8064</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>1.26</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3477</v>
+        <v>0.295</v>
       </c>
       <c r="J26" t="n">
-        <v>6.6063</v>
+        <v>5.605</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>0.99</v>
       </c>
       <c r="I27" t="n">
-        <v>0.0482</v>
+        <v>0.0708</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9157999999999999</v>
+        <v>1.3452</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0454</v>
+        <v>-0.0265</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.8626</v>
+        <v>-0.5034999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>0.82</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1911</v>
+        <v>-0.1751</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.6309</v>
+        <v>-3.3269</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.29</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.6708</v>
+        <v>-0.6958</v>
       </c>
       <c r="J30" t="n">
-        <v>-12.7452</v>
+        <v>-13.2202</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.21</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.7399</v>
+        <v>-0.78</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.0581</v>
+        <v>-14.82</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>1.36</v>
       </c>
       <c r="I32" t="n">
-        <v>0.656</v>
+        <v>0.6307</v>
       </c>
       <c r="J32" t="n">
-        <v>13.776</v>
+        <v>13.2447</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>0.98</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.0335</v>
+        <v>-0.026</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.7035</v>
+        <v>-0.546</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>0.73</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.3088</v>
+        <v>-0.2912</v>
       </c>
       <c r="J34" t="n">
-        <v>-6.4848</v>
+        <v>-6.1152</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>0.73</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.3088</v>
+        <v>-0.2912</v>
       </c>
       <c r="J35" t="n">
-        <v>-6.4848</v>
+        <v>-6.1152</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>0.63</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.4003</v>
+        <v>-0.3891</v>
       </c>
       <c r="J36" t="n">
-        <v>-8.4063</v>
+        <v>-8.171099999999999</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>1.61</v>
       </c>
       <c r="I37" t="n">
-        <v>1.0818</v>
+        <v>1.0724</v>
       </c>
       <c r="J37" t="n">
-        <v>22.7178</v>
+        <v>22.5204</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>1.44</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8556</v>
+        <v>0.8421</v>
       </c>
       <c r="J38" t="n">
-        <v>17.9676</v>
+        <v>17.6841</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>1.39</v>
       </c>
       <c r="I39" t="n">
-        <v>0.7867</v>
+        <v>0.7739</v>
       </c>
       <c r="J39" t="n">
-        <v>16.5207</v>
+        <v>16.2519</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.2926</v>
+        <v>0.2611</v>
       </c>
       <c r="J40" t="n">
-        <v>6.1446</v>
+        <v>5.4831</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.0518</v>
+        <v>-0.0474</v>
       </c>
       <c r="J41" t="n">
-        <v>-1.0878</v>
+        <v>-0.9954</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>1.36</v>
       </c>
       <c r="I42" t="n">
-        <v>0.6462</v>
+        <v>0.6193</v>
       </c>
       <c r="J42" t="n">
-        <v>17.4474</v>
+        <v>16.7211</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.95</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.0809</v>
+        <v>-0.0674</v>
       </c>
       <c r="J43" t="n">
-        <v>-2.1843</v>
+        <v>-1.8198</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.78</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.2643</v>
+        <v>-0.2449</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.1361</v>
+        <v>-6.6123</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.76</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2836</v>
+        <v>-0.2648</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.6572</v>
+        <v>-7.1496</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.74</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.3027</v>
+        <v>-0.2847</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.1729</v>
+        <v>-7.6869</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.58</v>
       </c>
       <c r="I47" t="n">
-        <v>1.0655</v>
+        <v>1.0557</v>
       </c>
       <c r="J47" t="n">
-        <v>28.7685</v>
+        <v>28.5039</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.48</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9293</v>
+        <v>0.9149</v>
       </c>
       <c r="J48" t="n">
-        <v>25.0911</v>
+        <v>24.7023</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.03</v>
       </c>
       <c r="I49" t="n">
-        <v>0.1041</v>
+        <v>0.0837</v>
       </c>
       <c r="J49" t="n">
-        <v>2.8107</v>
+        <v>2.2599</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>0.99</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.0934</v>
+        <v>-0.0725</v>
       </c>
       <c r="J50" t="n">
-        <v>-2.5218</v>
+        <v>-1.9575</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>0.92</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.3255</v>
+        <v>-0.2853</v>
       </c>
       <c r="J51" t="n">
-        <v>-8.788500000000001</v>
+        <v>-7.7031</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.59</v>
       </c>
       <c r="I52" t="n">
-        <v>1.0529</v>
+        <v>1.0425</v>
       </c>
       <c r="J52" t="n">
-        <v>24.2167</v>
+        <v>23.9775</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>1.44</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8535</v>
+        <v>0.8403</v>
       </c>
       <c r="J53" t="n">
-        <v>19.6305</v>
+        <v>19.3269</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>1.4</v>
       </c>
       <c r="I54" t="n">
-        <v>0.7987</v>
+        <v>0.7862</v>
       </c>
       <c r="J54" t="n">
-        <v>18.3701</v>
+        <v>18.0826</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>1.23</v>
       </c>
       <c r="I55" t="n">
-        <v>0.5535</v>
+        <v>0.5501</v>
       </c>
       <c r="J55" t="n">
-        <v>12.7305</v>
+        <v>12.6523</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.96</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.2261</v>
+        <v>-0.194</v>
       </c>
       <c r="J56" t="n">
-        <v>-5.2003</v>
+        <v>-4.462</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>1.24</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5413</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="J57" t="n">
-        <v>12.4499</v>
+        <v>12.0911</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>0.85</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.1835</v>
+        <v>-0.1671</v>
       </c>
       <c r="J58" t="n">
-        <v>-4.2205</v>
+        <v>-3.8433</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>0.78</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.2522</v>
+        <v>-0.235</v>
       </c>
       <c r="J59" t="n">
-        <v>-5.8006</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>0.66</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.3629</v>
+        <v>-0.3488</v>
       </c>
       <c r="J60" t="n">
-        <v>-8.3467</v>
+        <v>-8.022399999999999</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.42</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5732</v>
+        <v>-0.5829</v>
       </c>
       <c r="J61" t="n">
-        <v>-13.1836</v>
+        <v>-13.4067</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>2.13</v>
       </c>
       <c r="I62" t="n">
-        <v>1.723</v>
+        <v>1.7707</v>
       </c>
       <c r="J62" t="n">
-        <v>39.629</v>
+        <v>40.7261</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.52</v>
       </c>
       <c r="I63" t="n">
-        <v>0.9638</v>
+        <v>0.951</v>
       </c>
       <c r="J63" t="n">
-        <v>22.1674</v>
+        <v>21.873</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1.07</v>
       </c>
       <c r="I64" t="n">
-        <v>0.2111</v>
+        <v>0.1818</v>
       </c>
       <c r="J64" t="n">
-        <v>4.8553</v>
+        <v>4.1814</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.99</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1113</v>
+        <v>-0.0917</v>
       </c>
       <c r="J65" t="n">
-        <v>-2.5599</v>
+        <v>-2.1091</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.82</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5958</v>
+        <v>-0.5633</v>
       </c>
       <c r="J66" t="n">
-        <v>-13.7034</v>
+        <v>-12.9559</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>0.95</v>
       </c>
       <c r="I67" t="n">
-        <v>-0.0772</v>
+        <v>-0.0646</v>
       </c>
       <c r="J67" t="n">
-        <v>-1.7756</v>
+        <v>-1.4858</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>0.95</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.0772</v>
+        <v>-0.0646</v>
       </c>
       <c r="J68" t="n">
-        <v>-1.7756</v>
+        <v>-1.4858</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>0.95</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.0772</v>
+        <v>-0.0646</v>
       </c>
       <c r="J69" t="n">
-        <v>-1.7756</v>
+        <v>-1.4858</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>0.85</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.1908</v>
+        <v>-0.1718</v>
       </c>
       <c r="J70" t="n">
-        <v>-4.3884</v>
+        <v>-3.9514</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.7</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.3362</v>
+        <v>-0.32</v>
       </c>
       <c r="J71" t="n">
-        <v>-7.7326</v>
+        <v>-7.36</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.35</v>
       </c>
       <c r="I72" t="n">
-        <v>0.6758999999999999</v>
+        <v>0.6188</v>
       </c>
       <c r="J72" t="n">
-        <v>17.5734</v>
+        <v>16.0888</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.1</v>
       </c>
       <c r="I73" t="n">
-        <v>0.2528</v>
+        <v>0.2063</v>
       </c>
       <c r="J73" t="n">
-        <v>6.5728</v>
+        <v>5.3638</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.09</v>
       </c>
       <c r="I74" t="n">
-        <v>0.233</v>
+        <v>0.1884</v>
       </c>
       <c r="J74" t="n">
-        <v>6.058</v>
+        <v>4.8984</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>0.83</v>
       </c>
       <c r="I75" t="n">
-        <v>-0.222</v>
+        <v>-0.2015</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.772</v>
+        <v>-5.239</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.62</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.4195</v>
+        <v>-0.4113</v>
       </c>
       <c r="J76" t="n">
-        <v>-10.907</v>
+        <v>-10.6938</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.46</v>
       </c>
       <c r="I77" t="n">
-        <v>1.0486</v>
+        <v>1.0538</v>
       </c>
       <c r="J77" t="n">
-        <v>27.2636</v>
+        <v>27.3988</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.34</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8339</v>
+        <v>0.8117</v>
       </c>
       <c r="J78" t="n">
-        <v>21.6814</v>
+        <v>21.1042</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.27</v>
       </c>
       <c r="I79" t="n">
-        <v>0.6925</v>
+        <v>0.6622</v>
       </c>
       <c r="J79" t="n">
-        <v>18.005</v>
+        <v>17.2172</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>1.03</v>
       </c>
       <c r="I80" t="n">
-        <v>0.1048</v>
+        <v>0.0844</v>
       </c>
       <c r="J80" t="n">
-        <v>2.7248</v>
+        <v>2.1944</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.88</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4316</v>
+        <v>-0.3907</v>
       </c>
       <c r="J81" t="n">
-        <v>-11.2216</v>
+        <v>-10.1582</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.37</v>
       </c>
       <c r="I82" t="n">
-        <v>0.7374000000000001</v>
+        <v>0.6881</v>
       </c>
       <c r="J82" t="n">
-        <v>18.435</v>
+        <v>17.2025</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>0.98</v>
       </c>
       <c r="I83" t="n">
-        <v>-0.0364</v>
+        <v>-0.0285</v>
       </c>
       <c r="J83" t="n">
-        <v>-0.91</v>
+        <v>-0.7125</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.9</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.1399</v>
+        <v>-0.1221</v>
       </c>
       <c r="J84" t="n">
-        <v>-3.4975</v>
+        <v>-3.0525</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.68</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.3578</v>
+        <v>-0.3432</v>
       </c>
       <c r="J85" t="n">
-        <v>-8.945</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.63</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.4029</v>
+        <v>-0.3921</v>
       </c>
       <c r="J86" t="n">
-        <v>-10.0725</v>
+        <v>-9.8025</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.46</v>
       </c>
       <c r="I87" t="n">
-        <v>1.0478</v>
+        <v>1.0529</v>
       </c>
       <c r="J87" t="n">
-        <v>26.195</v>
+        <v>26.3225</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.37</v>
       </c>
       <c r="I88" t="n">
-        <v>0.892</v>
+        <v>0.8743</v>
       </c>
       <c r="J88" t="n">
-        <v>22.3</v>
+        <v>21.8575</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.07</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2287</v>
+        <v>0.199</v>
       </c>
       <c r="J89" t="n">
-        <v>5.7175</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.07</v>
       </c>
       <c r="I90" t="n">
-        <v>0.2287</v>
+        <v>0.199</v>
       </c>
       <c r="J90" t="n">
-        <v>5.7175</v>
+        <v>4.975</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>1.03</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1041</v>
+        <v>0.0837</v>
       </c>
       <c r="J91" t="n">
-        <v>2.6025</v>
+        <v>2.0925</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.06</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1896</v>
+        <v>0.1496</v>
       </c>
       <c r="J92" t="n">
-        <v>4.74</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.01</v>
       </c>
       <c r="I93" t="n">
-        <v>0.059</v>
+        <v>0.0407</v>
       </c>
       <c r="J93" t="n">
-        <v>1.475</v>
+        <v>1.0175</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>0.98</v>
       </c>
       <c r="I94" t="n">
-        <v>-0.0354</v>
+        <v>-0.0276</v>
       </c>
       <c r="J94" t="n">
-        <v>-0.885</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.78</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.2627</v>
+        <v>-0.2434</v>
       </c>
       <c r="J95" t="n">
-        <v>-6.5675</v>
+        <v>-6.085</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.68</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.3568</v>
+        <v>-0.3421</v>
       </c>
       <c r="J96" t="n">
-        <v>-8.92</v>
+        <v>-8.5525</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>2.03</v>
       </c>
       <c r="I97" t="n">
-        <v>1.7595</v>
+        <v>1.8199</v>
       </c>
       <c r="J97" t="n">
-        <v>43.9875</v>
+        <v>45.4975</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.26</v>
       </c>
       <c r="I98" t="n">
-        <v>0.662</v>
+        <v>0.635</v>
       </c>
       <c r="J98" t="n">
-        <v>16.55</v>
+        <v>15.875</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.14</v>
       </c>
       <c r="I99" t="n">
-        <v>0.3975</v>
+        <v>0.3652</v>
       </c>
       <c r="J99" t="n">
-        <v>9.9375</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>1.06</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1862</v>
+        <v>0.1585</v>
       </c>
       <c r="J100" t="n">
-        <v>4.655</v>
+        <v>3.9625</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.91</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3667</v>
+        <v>-0.3279</v>
       </c>
       <c r="J101" t="n">
-        <v>-9.1675</v>
+        <v>-8.1975</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.66</v>
       </c>
       <c r="I102" t="n">
-        <v>1.3273</v>
+        <v>1.3503</v>
       </c>
       <c r="J102" t="n">
-        <v>39.819</v>
+        <v>40.509</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.47</v>
       </c>
       <c r="I103" t="n">
-        <v>1.069</v>
+        <v>1.0771</v>
       </c>
       <c r="J103" t="n">
-        <v>32.07</v>
+        <v>32.313</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.09</v>
       </c>
       <c r="I104" t="n">
-        <v>0.2887</v>
+        <v>0.2559</v>
       </c>
       <c r="J104" t="n">
-        <v>8.661</v>
+        <v>7.677</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>0.96</v>
       </c>
       <c r="I105" t="n">
-        <v>-0.2</v>
+        <v>-0.1654</v>
       </c>
       <c r="J105" t="n">
-        <v>-6</v>
+        <v>-4.962</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.67</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.9031</v>
+        <v>-0.8925</v>
       </c>
       <c r="J106" t="n">
-        <v>-27.093</v>
+        <v>-26.775</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.08</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2236</v>
+        <v>0.1795</v>
       </c>
       <c r="J107" t="n">
-        <v>6.708</v>
+        <v>5.385</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>0.98</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.0393</v>
+        <v>-0.0306</v>
       </c>
       <c r="J108" t="n">
-        <v>-1.179</v>
+        <v>-0.918</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.0951</v>
+        <v>-0.07969999999999999</v>
       </c>
       <c r="J109" t="n">
-        <v>-2.853</v>
+        <v>-2.391</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.92</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1191</v>
+        <v>-0.1018</v>
       </c>
       <c r="J110" t="n">
-        <v>-3.573</v>
+        <v>-3.054</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.79</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2569</v>
+        <v>-0.2371</v>
       </c>
       <c r="J111" t="n">
-        <v>-7.707</v>
+        <v>-7.113</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.36</v>
       </c>
       <c r="I112" t="n">
-        <v>0.7266</v>
+        <v>0.6778</v>
       </c>
       <c r="J112" t="n">
-        <v>16.7118</v>
+        <v>15.5894</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>1.04</v>
       </c>
       <c r="I113" t="n">
-        <v>0.1432</v>
+        <v>0.1093</v>
       </c>
       <c r="J113" t="n">
-        <v>3.2936</v>
+        <v>2.5139</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.85</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.1925</v>
+        <v>-0.1729</v>
       </c>
       <c r="J114" t="n">
-        <v>-4.4275</v>
+        <v>-3.9767</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.73</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.3103</v>
+        <v>-0.2927</v>
       </c>
       <c r="J115" t="n">
-        <v>-7.1369</v>
+        <v>-6.7321</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.52</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.4979</v>
+        <v>-0.498</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.4517</v>
+        <v>-11.454</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.58</v>
       </c>
       <c r="I117" t="n">
-        <v>1.1986</v>
+        <v>1.2133</v>
       </c>
       <c r="J117" t="n">
-        <v>27.5678</v>
+        <v>27.9059</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.5</v>
       </c>
       <c r="I118" t="n">
-        <v>1.0916</v>
+        <v>1.1025</v>
       </c>
       <c r="J118" t="n">
-        <v>25.1068</v>
+        <v>25.3575</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.22</v>
       </c>
       <c r="I119" t="n">
-        <v>0.5809</v>
+        <v>0.5507</v>
       </c>
       <c r="J119" t="n">
-        <v>13.3607</v>
+        <v>12.6661</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.03</v>
       </c>
       <c r="I120" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.0727</v>
       </c>
       <c r="J120" t="n">
-        <v>2.1436</v>
+        <v>1.6721</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.99</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1044</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.4012</v>
+        <v>-1.9343</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.11</v>
       </c>
       <c r="I122" t="n">
-        <v>0.2832</v>
+        <v>0.2338</v>
       </c>
       <c r="J122" t="n">
-        <v>10.1952</v>
+        <v>8.4168</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.02</v>
       </c>
       <c r="I123" t="n">
-        <v>0.08119999999999999</v>
+        <v>0.0578</v>
       </c>
       <c r="J123" t="n">
-        <v>2.9232</v>
+        <v>2.0808</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>0.9</v>
       </c>
       <c r="I124" t="n">
-        <v>-0.1424</v>
+        <v>-0.1237</v>
       </c>
       <c r="J124" t="n">
-        <v>-5.1264</v>
+        <v>-4.4532</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.87</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1754</v>
+        <v>-0.1555</v>
       </c>
       <c r="J125" t="n">
-        <v>-6.3144</v>
+        <v>-5.598</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.83</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2172</v>
+        <v>-0.1969</v>
       </c>
       <c r="J126" t="n">
-        <v>-7.8192</v>
+        <v>-7.0884</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.45</v>
       </c>
       <c r="I127" t="n">
-        <v>1.0428</v>
+        <v>1.0471</v>
       </c>
       <c r="J127" t="n">
-        <v>37.5408</v>
+        <v>37.6956</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>1.17</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4839</v>
+        <v>0.447</v>
       </c>
       <c r="J128" t="n">
-        <v>17.4204</v>
+        <v>16.092</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>1.11</v>
       </c>
       <c r="I129" t="n">
-        <v>0.3427</v>
+        <v>0.3077</v>
       </c>
       <c r="J129" t="n">
-        <v>12.3372</v>
+        <v>11.0772</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>1.05</v>
       </c>
       <c r="I130" t="n">
-        <v>0.177</v>
+        <v>0.1501</v>
       </c>
       <c r="J130" t="n">
-        <v>6.372</v>
+        <v>5.4036</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>1</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.0257</v>
+        <v>-0.0203</v>
       </c>
       <c r="J131" t="n">
-        <v>-0.9252</v>
+        <v>-0.7308</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.42</v>
       </c>
       <c r="I132" t="n">
-        <v>1.0209</v>
+        <v>1.0229</v>
       </c>
       <c r="J132" t="n">
-        <v>36.7524</v>
+        <v>36.8244</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.11</v>
       </c>
       <c r="I133" t="n">
-        <v>0.3545</v>
+        <v>0.3145</v>
       </c>
       <c r="J133" t="n">
-        <v>12.762</v>
+        <v>11.322</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>0.98</v>
       </c>
       <c r="I134" t="n">
-        <v>-0.1102</v>
+        <v>-0.0843</v>
       </c>
       <c r="J134" t="n">
-        <v>-3.9672</v>
+        <v>-3.0348</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>0.97</v>
       </c>
       <c r="I135" t="n">
-        <v>-0.1466</v>
+        <v>-0.1162</v>
       </c>
       <c r="J135" t="n">
-        <v>-5.2776</v>
+        <v>-4.1832</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.84</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.5063</v>
+        <v>-0.4645</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.2268</v>
+        <v>-16.722</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.65</v>
       </c>
       <c r="I137" t="n">
-        <v>1.0518</v>
+        <v>1.0279</v>
       </c>
       <c r="J137" t="n">
-        <v>37.8648</v>
+        <v>37.0044</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.19</v>
       </c>
       <c r="I138" t="n">
-        <v>0.3963</v>
+        <v>0.3417</v>
       </c>
       <c r="J138" t="n">
-        <v>14.2668</v>
+        <v>12.3012</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>1.08</v>
       </c>
       <c r="I139" t="n">
-        <v>0.2002</v>
+        <v>0.1627</v>
       </c>
       <c r="J139" t="n">
-        <v>7.2072</v>
+        <v>5.8572</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>1.06</v>
       </c>
       <c r="I140" t="n">
-        <v>0.1587</v>
+        <v>0.1264</v>
       </c>
       <c r="J140" t="n">
-        <v>5.7132</v>
+        <v>4.5504</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.4796</v>
+        <v>-0.48</v>
       </c>
       <c r="J141" t="n">
-        <v>-17.2656</v>
+        <v>-17.28</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.23</v>
       </c>
       <c r="I142" t="n">
-        <v>1.9372</v>
+        <v>1.9818</v>
       </c>
       <c r="J142" t="n">
-        <v>40.6812</v>
+        <v>41.6178</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>1.54</v>
       </c>
       <c r="I143" t="n">
-        <v>1.1214</v>
+        <v>1.1367</v>
       </c>
       <c r="J143" t="n">
-        <v>23.5494</v>
+        <v>23.8707</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.26</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6435</v>
+        <v>0.6206</v>
       </c>
       <c r="J144" t="n">
-        <v>13.5135</v>
+        <v>13.0326</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.1</v>
       </c>
       <c r="I145" t="n">
-        <v>0.2756</v>
+        <v>0.2432</v>
       </c>
       <c r="J145" t="n">
-        <v>5.7876</v>
+        <v>5.1072</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.96</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.2402</v>
+        <v>-0.2107</v>
       </c>
       <c r="J146" t="n">
-        <v>-5.0442</v>
+        <v>-4.4247</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.96</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0465</v>
+        <v>-0.0353</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.9765</v>
+        <v>-0.7413</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.82</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.2121</v>
+        <v>-0.1958</v>
       </c>
       <c r="J148" t="n">
-        <v>-4.4541</v>
+        <v>-4.1118</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.79</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.2416</v>
+        <v>-0.2251</v>
       </c>
       <c r="J149" t="n">
-        <v>-5.0736</v>
+        <v>-4.7271</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.67</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.3516</v>
+        <v>-0.337</v>
       </c>
       <c r="J150" t="n">
-        <v>-7.3836</v>
+        <v>-7.077</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.61</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.4055</v>
+        <v>-0.3945</v>
       </c>
       <c r="J151" t="n">
-        <v>-8.515499999999999</v>
+        <v>-8.2845</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>1.66</v>
       </c>
       <c r="I152" t="n">
-        <v>1.0966</v>
+        <v>1.0884</v>
       </c>
       <c r="J152" t="n">
-        <v>31.8014</v>
+        <v>31.5636</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>1.03</v>
       </c>
       <c r="I153" t="n">
-        <v>0.1013</v>
+        <v>0.0747</v>
       </c>
       <c r="J153" t="n">
-        <v>2.9377</v>
+        <v>2.1663</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.99</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.0248</v>
+        <v>-0.018</v>
       </c>
       <c r="J154" t="n">
-        <v>-0.7192</v>
+        <v>-0.522</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.8</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.2515</v>
+        <v>-0.2316</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.2935</v>
+        <v>-6.7164</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.47</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.5474</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>-15.8746</v>
+        <v>-16.1211</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.59</v>
       </c>
       <c r="I157" t="n">
-        <v>1.283</v>
+        <v>1.3107</v>
       </c>
       <c r="J157" t="n">
-        <v>37.207</v>
+        <v>38.0103</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.1</v>
       </c>
       <c r="I158" t="n">
-        <v>0.3378</v>
+        <v>0.2965</v>
       </c>
       <c r="J158" t="n">
-        <v>9.796200000000001</v>
+        <v>8.5985</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.07</v>
       </c>
       <c r="I159" t="n">
-        <v>0.2558</v>
+        <v>0.2181</v>
       </c>
       <c r="J159" t="n">
-        <v>7.4182</v>
+        <v>6.3249</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>0.68</v>
       </c>
       <c r="I160" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.8355</v>
       </c>
       <c r="J160" t="n">
-        <v>-24.8037</v>
+        <v>-24.2295</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>0.65</v>
       </c>
       <c r="I161" t="n">
-        <v>-0.9181</v>
+        <v>-0.905</v>
       </c>
       <c r="J161" t="n">
-        <v>-26.6249</v>
+        <v>-26.245</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.7</v>
       </c>
       <c r="I162" t="n">
-        <v>1.3334</v>
+        <v>1.3545</v>
       </c>
       <c r="J162" t="n">
-        <v>32.0016</v>
+        <v>32.508</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.51</v>
       </c>
       <c r="I163" t="n">
-        <v>1.0891</v>
+        <v>1.1019</v>
       </c>
       <c r="J163" t="n">
-        <v>26.1384</v>
+        <v>26.4456</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.37</v>
       </c>
       <c r="I164" t="n">
-        <v>0.865</v>
+        <v>0.8526</v>
       </c>
       <c r="J164" t="n">
-        <v>20.76</v>
+        <v>20.4624</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.17</v>
       </c>
       <c r="I165" t="n">
-        <v>0.4552</v>
+        <v>0.4245</v>
       </c>
       <c r="J165" t="n">
-        <v>10.9248</v>
+        <v>10.188</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>1.07</v>
       </c>
       <c r="I166" t="n">
-        <v>0.2019</v>
+        <v>0.1721</v>
       </c>
       <c r="J166" t="n">
-        <v>4.8456</v>
+        <v>4.1304</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>0.96</v>
       </c>
       <c r="I167" t="n">
-        <v>-0.0488</v>
+        <v>-0.0378</v>
       </c>
       <c r="J167" t="n">
-        <v>-1.1712</v>
+        <v>-0.9072</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>0.89</v>
       </c>
       <c r="I168" t="n">
-        <v>-0.1383</v>
+        <v>-0.123</v>
       </c>
       <c r="J168" t="n">
-        <v>-3.3192</v>
+        <v>-2.952</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.83</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.2033</v>
+        <v>-0.1869</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.8792</v>
+        <v>-4.4856</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.65</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.3711</v>
+        <v>-0.3575</v>
       </c>
       <c r="J170" t="n">
-        <v>-8.9064</v>
+        <v>-8.58</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.58</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.4336</v>
+        <v>-0.425</v>
       </c>
       <c r="J171" t="n">
-        <v>-10.4064</v>
+        <v>-10.2</v>
       </c>
     </row>
   </sheetData>
